--- a/scripts/census_acs/inputs/acs_variables.xlsx
+++ b/scripts/census_acs/inputs/acs_variables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20416"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\_geodata\data_public\ossdb\processing\geodata_ossdb\scripts\census_acs\inputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="N:\Library_Shared\_geodata\data_public\ossdb\processing\geodata_ossdb\scripts\census_acs\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F84B067B-3030-4DC4-A36E-D9DE1D80C4AC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0457C4A7-A93F-4782-A216-2A06E6DDD5A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="readme" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10486" uniqueCount="4652">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10486" uniqueCount="4692">
   <si>
     <t>Second set of ACS variables from DP04 and DP05, correlates nycgdb column names with census names, labels, and types from the API</t>
   </si>
@@ -13942,52 +13942,172 @@
     <t>Percent Margin of Error!!HISPANIC OR LATINO AND RACE!!Total population!!Not Hispanic or Latino!!Two or More Races</t>
   </si>
   <si>
-    <t>Estimate!!INCOME AND BENEFITS (IN 2023 INFLATION-ADJUSTED DOLLARS)!!Total households</t>
-  </si>
-  <si>
-    <t>Margin of Error!!INCOME AND BENEFITS (IN 2023 INFLATION-ADJUSTED DOLLARS)!!Total households</t>
-  </si>
-  <si>
-    <t>Percent!!INCOME AND BENEFITS (IN 2023 INFLATION-ADJUSTED DOLLARS)!!Total households</t>
-  </si>
-  <si>
-    <t>Percent Margin of Error!!INCOME AND BENEFITS (IN 2023 INFLATION-ADJUSTED DOLLARS)!!Total households</t>
-  </si>
-  <si>
-    <t>Estimate!!INCOME AND BENEFITS (IN 2023 INFLATION-ADJUSTED DOLLARS)!!Total households!!Median household income (dollars)</t>
-  </si>
-  <si>
-    <t>Margin of Error!!INCOME AND BENEFITS (IN 2023 INFLATION-ADJUSTED DOLLARS)!!Total households!!Median household income (dollars)</t>
-  </si>
-  <si>
-    <t>Percent!!INCOME AND BENEFITS (IN 2023 INFLATION-ADJUSTED DOLLARS)!!Total households!!Median household income (dollars)</t>
-  </si>
-  <si>
-    <t>Percent Margin of Error!!INCOME AND BENEFITS (IN 2023 INFLATION-ADJUSTED DOLLARS)!!Total households!!Median household income (dollars)</t>
-  </si>
-  <si>
-    <t>Estimate!!INCOME AND BENEFITS (IN 2023 INFLATION-ADJUSTED DOLLARS)!!Total households!!Mean household income (dollars)</t>
-  </si>
-  <si>
-    <t>Margin of Error!!INCOME AND BENEFITS (IN 2023 INFLATION-ADJUSTED DOLLARS)!!Total households!!Mean household income (dollars)</t>
-  </si>
-  <si>
-    <t>Percent!!INCOME AND BENEFITS (IN 2023 INFLATION-ADJUSTED DOLLARS)!!Total households!!Mean household income (dollars)</t>
-  </si>
-  <si>
-    <t>Percent Margin of Error!!INCOME AND BENEFITS (IN 2023 INFLATION-ADJUSTED DOLLARS)!!Total households!!Mean household income (dollars)</t>
-  </si>
-  <si>
-    <t>DP05_0092E</t>
-  </si>
-  <si>
-    <t>DP05_0092M</t>
-  </si>
-  <si>
-    <t>DP05_0092PE</t>
-  </si>
-  <si>
-    <t>DP05_0092PM</t>
+    <t>Estimate!!COMMUTING TO WORK!!Workers 16 years and over!!Public transportation</t>
+  </si>
+  <si>
+    <t>Margin of Error!!COMMUTING TO WORK!!Workers 16 years and over!!Public transportation</t>
+  </si>
+  <si>
+    <t>Percent!!COMMUTING TO WORK!!Workers 16 years and over!!Public transportation</t>
+  </si>
+  <si>
+    <t>Percent Margin of Error!!COMMUTING TO WORK!!Workers 16 years and over!!Public transportation</t>
+  </si>
+  <si>
+    <t>Estimate!!INCOME AND BENEFITS (IN 2024 INFLATION-ADJUSTED DOLLARS)!!Total households</t>
+  </si>
+  <si>
+    <t>Margin of Error!!INCOME AND BENEFITS (IN 2024 INFLATION-ADJUSTED DOLLARS)!!Total households</t>
+  </si>
+  <si>
+    <t>Percent!!INCOME AND BENEFITS (IN 2024 INFLATION-ADJUSTED DOLLARS)!!Total households</t>
+  </si>
+  <si>
+    <t>Percent Margin of Error!!INCOME AND BENEFITS (IN 2024 INFLATION-ADJUSTED DOLLARS)!!Total households</t>
+  </si>
+  <si>
+    <t>Estimate!!INCOME AND BENEFITS (IN 2024 INFLATION-ADJUSTED DOLLARS)!!Total households!!Median household income (dollars)</t>
+  </si>
+  <si>
+    <t>Margin of Error!!INCOME AND BENEFITS (IN 2024 INFLATION-ADJUSTED DOLLARS)!!Total households!!Median household income (dollars)</t>
+  </si>
+  <si>
+    <t>Percent!!INCOME AND BENEFITS (IN 2024 INFLATION-ADJUSTED DOLLARS)!!Total households!!Median household income (dollars)</t>
+  </si>
+  <si>
+    <t>Percent Margin of Error!!INCOME AND BENEFITS (IN 2024 INFLATION-ADJUSTED DOLLARS)!!Total households!!Median household income (dollars)</t>
+  </si>
+  <si>
+    <t>Estimate!!INCOME AND BENEFITS (IN 2024 INFLATION-ADJUSTED DOLLARS)!!Total households!!Mean household income (dollars)</t>
+  </si>
+  <si>
+    <t>Margin of Error!!INCOME AND BENEFITS (IN 2024 INFLATION-ADJUSTED DOLLARS)!!Total households!!Mean household income (dollars)</t>
+  </si>
+  <si>
+    <t>Percent!!INCOME AND BENEFITS (IN 2024 INFLATION-ADJUSTED DOLLARS)!!Total households!!Mean household income (dollars)</t>
+  </si>
+  <si>
+    <t>Percent Margin of Error!!INCOME AND BENEFITS (IN 2024 INFLATION-ADJUSTED DOLLARS)!!Total households!!Mean household income (dollars)</t>
+  </si>
+  <si>
+    <t>DP05_0090E</t>
+  </si>
+  <si>
+    <t>DP05_0090M</t>
+  </si>
+  <si>
+    <t>DP05_0090PE</t>
+  </si>
+  <si>
+    <t>DP05_0090PM</t>
+  </si>
+  <si>
+    <t>DP05_0095E</t>
+  </si>
+  <si>
+    <t>DP05_0095M</t>
+  </si>
+  <si>
+    <t>DP05_0095PE</t>
+  </si>
+  <si>
+    <t>DP05_0095PM</t>
+  </si>
+  <si>
+    <t>DP05_0096E</t>
+  </si>
+  <si>
+    <t>DP05_0096M</t>
+  </si>
+  <si>
+    <t>DP05_0096PE</t>
+  </si>
+  <si>
+    <t>DP05_0096PM</t>
+  </si>
+  <si>
+    <t>DP05_0097E</t>
+  </si>
+  <si>
+    <t>DP05_0097M</t>
+  </si>
+  <si>
+    <t>DP05_0097PE</t>
+  </si>
+  <si>
+    <t>DP05_0097PM</t>
+  </si>
+  <si>
+    <t>DP05_0098E</t>
+  </si>
+  <si>
+    <t>DP05_0098M</t>
+  </si>
+  <si>
+    <t>DP05_0098PE</t>
+  </si>
+  <si>
+    <t>DP05_0098PM</t>
+  </si>
+  <si>
+    <t>DP05_0099E</t>
+  </si>
+  <si>
+    <t>DP05_0099M</t>
+  </si>
+  <si>
+    <t>DP05_0099PE</t>
+  </si>
+  <si>
+    <t>DP05_0099PM</t>
+  </si>
+  <si>
+    <t>DP05_0100E</t>
+  </si>
+  <si>
+    <t>DP05_0100M</t>
+  </si>
+  <si>
+    <t>DP05_0100PE</t>
+  </si>
+  <si>
+    <t>DP05_0100PM</t>
+  </si>
+  <si>
+    <t>DP05_0101E</t>
+  </si>
+  <si>
+    <t>DP05_0101M</t>
+  </si>
+  <si>
+    <t>DP05_0101PE</t>
+  </si>
+  <si>
+    <t>DP05_0101PM</t>
+  </si>
+  <si>
+    <t>DP05_0102E</t>
+  </si>
+  <si>
+    <t>DP05_0102M</t>
+  </si>
+  <si>
+    <t>DP05_0102PE</t>
+  </si>
+  <si>
+    <t>DP05_0102PM</t>
+  </si>
+  <si>
+    <t>DP05_0106E</t>
+  </si>
+  <si>
+    <t>DP05_0106M</t>
+  </si>
+  <si>
+    <t>DP05_0106PE</t>
+  </si>
+  <si>
+    <t>DP05_0106PM</t>
   </si>
 </sst>
 </file>
@@ -14035,7 +14155,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -14415,7 +14535,7 @@
   <dimension ref="A1:D189"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.21875" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="75.33203125" customWidth="1"/>
   </cols>
@@ -14435,7 +14555,7 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" t="s">
         <v>7</v>
       </c>
       <c r="B2" t="s">
@@ -14449,7 +14569,7 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" t="s">
         <v>11</v>
       </c>
       <c r="B3" t="s">
@@ -14463,7 +14583,7 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+      <c r="A4" t="s">
         <v>4535</v>
       </c>
       <c r="B4" t="s">
@@ -14477,7 +14597,7 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+      <c r="A5" t="s">
         <v>15</v>
       </c>
       <c r="B5" t="s">
@@ -14491,7 +14611,7 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
+      <c r="A6" t="s">
         <v>18</v>
       </c>
       <c r="B6" t="s">
@@ -14505,7 +14625,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
+      <c r="A7" t="s">
         <v>20</v>
       </c>
       <c r="B7" t="s">
@@ -14519,7 +14639,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
+      <c r="A8" t="s">
         <v>4536</v>
       </c>
       <c r="B8" t="s">
@@ -14533,7 +14653,7 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
+      <c r="A9" t="s">
         <v>24</v>
       </c>
       <c r="B9" t="s">
@@ -14547,7 +14667,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
+      <c r="A10" t="s">
         <v>44</v>
       </c>
       <c r="B10" t="s">
@@ -14561,7 +14681,7 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
+      <c r="A11" t="s">
         <v>47</v>
       </c>
       <c r="B11" t="s">
@@ -14575,7 +14695,7 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
+      <c r="A12" t="s">
         <v>4537</v>
       </c>
       <c r="B12" t="s">
@@ -14589,7 +14709,7 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
+      <c r="A13" t="s">
         <v>51</v>
       </c>
       <c r="B13" t="s">
@@ -14603,7 +14723,7 @@
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
+      <c r="A14" t="s">
         <v>54</v>
       </c>
       <c r="B14" t="s">
@@ -14617,7 +14737,7 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
+      <c r="A15" t="s">
         <v>57</v>
       </c>
       <c r="B15" t="s">
@@ -14631,7 +14751,7 @@
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
+      <c r="A16" t="s">
         <v>4538</v>
       </c>
       <c r="B16" t="s">
@@ -14645,7 +14765,7 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
+      <c r="A17" t="s">
         <v>61</v>
       </c>
       <c r="B17" t="s">
@@ -14659,7 +14779,7 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
+      <c r="A18" t="s">
         <v>64</v>
       </c>
       <c r="B18" t="s">
@@ -14673,7 +14793,7 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
+      <c r="A19" t="s">
         <v>66</v>
       </c>
       <c r="B19" t="s">
@@ -14687,7 +14807,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="s">
+      <c r="A20" t="s">
         <v>4539</v>
       </c>
       <c r="B20" t="s">
@@ -14701,7 +14821,7 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="3" t="s">
+      <c r="A21" t="s">
         <v>69</v>
       </c>
       <c r="B21" t="s">
@@ -14715,7 +14835,7 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="3" t="s">
+      <c r="A22" t="s">
         <v>71</v>
       </c>
       <c r="B22" t="s">
@@ -14729,7 +14849,7 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="3" t="s">
+      <c r="A23" t="s">
         <v>74</v>
       </c>
       <c r="B23" t="s">
@@ -14743,7 +14863,7 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="3" t="s">
+      <c r="A24" t="s">
         <v>4540</v>
       </c>
       <c r="B24" t="s">
@@ -14757,7 +14877,7 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="3" t="s">
+      <c r="A25" t="s">
         <v>78</v>
       </c>
       <c r="B25" t="s">
@@ -14771,7 +14891,7 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="3" t="s">
+      <c r="A26" t="s">
         <v>81</v>
       </c>
       <c r="B26" t="s">
@@ -14785,7 +14905,7 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="3" t="s">
+      <c r="A27" t="s">
         <v>84</v>
       </c>
       <c r="B27" t="s">
@@ -14799,7 +14919,7 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="3" t="s">
+      <c r="A28" t="s">
         <v>4541</v>
       </c>
       <c r="B28" t="s">
@@ -14813,7 +14933,7 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="3" t="s">
+      <c r="A29" t="s">
         <v>88</v>
       </c>
       <c r="B29" t="s">
@@ -14827,7 +14947,7 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="3" t="s">
+      <c r="A30" t="s">
         <v>91</v>
       </c>
       <c r="B30" t="s">
@@ -14841,7 +14961,7 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="3" t="s">
+      <c r="A31" t="s">
         <v>94</v>
       </c>
       <c r="B31" t="s">
@@ -14855,7 +14975,7 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="3" t="s">
+      <c r="A32" t="s">
         <v>4542</v>
       </c>
       <c r="B32" t="s">
@@ -14869,7 +14989,7 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="3" t="s">
+      <c r="A33" t="s">
         <v>98</v>
       </c>
       <c r="B33" t="s">
@@ -14883,7 +15003,7 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="3" t="s">
+      <c r="A34" t="s">
         <v>101</v>
       </c>
       <c r="B34" t="s">
@@ -14897,7 +15017,7 @@
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="3" t="s">
+      <c r="A35" t="s">
         <v>104</v>
       </c>
       <c r="B35" t="s">
@@ -14911,7 +15031,7 @@
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="3" t="s">
+      <c r="A36" t="s">
         <v>4543</v>
       </c>
       <c r="B36" t="s">
@@ -14925,7 +15045,7 @@
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="3" t="s">
+      <c r="A37" t="s">
         <v>108</v>
       </c>
       <c r="B37" t="s">
@@ -14939,7 +15059,7 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="3" t="s">
+      <c r="A38" t="s">
         <v>111</v>
       </c>
       <c r="B38" t="s">
@@ -14953,7 +15073,7 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="3" t="s">
+      <c r="A39" t="s">
         <v>114</v>
       </c>
       <c r="B39" t="s">
@@ -14967,7 +15087,7 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="3" t="s">
+      <c r="A40" t="s">
         <v>4544</v>
       </c>
       <c r="B40" t="s">
@@ -14981,7 +15101,7 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" s="3" t="s">
+      <c r="A41" t="s">
         <v>118</v>
       </c>
       <c r="B41" t="s">
@@ -14995,7 +15115,7 @@
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" s="3" t="s">
+      <c r="A42" t="s">
         <v>121</v>
       </c>
       <c r="B42" t="s">
@@ -15009,7 +15129,7 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" s="3" t="s">
+      <c r="A43" t="s">
         <v>122</v>
       </c>
       <c r="B43" t="s">
@@ -15023,7 +15143,7 @@
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" s="3" t="s">
+      <c r="A44" t="s">
         <v>4545</v>
       </c>
       <c r="B44" t="s">
@@ -15037,7 +15157,7 @@
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" s="3" t="s">
+      <c r="A45" t="s">
         <v>123</v>
       </c>
       <c r="B45" t="s">
@@ -15051,7 +15171,7 @@
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46" s="3" t="s">
+      <c r="A46" t="s">
         <v>124</v>
       </c>
       <c r="B46" t="s">
@@ -15065,7 +15185,7 @@
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47" s="3" t="s">
+      <c r="A47" t="s">
         <v>125</v>
       </c>
       <c r="B47" t="s">
@@ -15079,7 +15199,7 @@
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" s="3" t="s">
+      <c r="A48" t="s">
         <v>4546</v>
       </c>
       <c r="B48" t="s">
@@ -15093,7 +15213,7 @@
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A49" s="3" t="s">
+      <c r="A49" t="s">
         <v>126</v>
       </c>
       <c r="B49" t="s">
@@ -15107,7 +15227,7 @@
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A50" s="3" t="s">
+      <c r="A50" t="s">
         <v>855</v>
       </c>
       <c r="B50" t="s">
@@ -15121,7 +15241,7 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A51" s="3" t="s">
+      <c r="A51" t="s">
         <v>857</v>
       </c>
       <c r="B51" t="s">
@@ -15135,7 +15255,7 @@
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A52" s="3" t="s">
+      <c r="A52" t="s">
         <v>4547</v>
       </c>
       <c r="B52" t="s">
@@ -15149,7 +15269,7 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A53" s="3" t="s">
+      <c r="A53" t="s">
         <v>858</v>
       </c>
       <c r="B53" t="s">
@@ -15163,7 +15283,7 @@
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A54" s="3" t="s">
+      <c r="A54" t="s">
         <v>856</v>
       </c>
       <c r="B54" t="s">
@@ -15177,7 +15297,7 @@
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A55" s="3" t="s">
+      <c r="A55" t="s">
         <v>4548</v>
       </c>
       <c r="B55" t="s">
@@ -15191,7 +15311,7 @@
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A56" s="3" t="s">
+      <c r="A56" t="s">
         <v>4549</v>
       </c>
       <c r="B56" t="s">
@@ -15205,7 +15325,7 @@
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A57" s="3" t="s">
+      <c r="A57" t="s">
         <v>859</v>
       </c>
       <c r="B57" t="s">
@@ -15219,7 +15339,7 @@
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58" s="3" t="s">
+      <c r="A58" t="s">
         <v>135</v>
       </c>
       <c r="B58" t="s">
@@ -15233,7 +15353,7 @@
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A59" s="3" t="s">
+      <c r="A59" t="s">
         <v>138</v>
       </c>
       <c r="B59" t="s">
@@ -15247,7 +15367,7 @@
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A60" s="3" t="s">
+      <c r="A60" t="s">
         <v>4550</v>
       </c>
       <c r="B60" t="s">
@@ -15261,7 +15381,7 @@
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A61" s="3" t="s">
+      <c r="A61" t="s">
         <v>142</v>
       </c>
       <c r="B61" t="s">
@@ -15275,7 +15395,7 @@
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A62" s="3" t="s">
+      <c r="A62" t="s">
         <v>145</v>
       </c>
       <c r="B62" t="s">
@@ -15289,7 +15409,7 @@
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A63" s="3" t="s">
+      <c r="A63" t="s">
         <v>148</v>
       </c>
       <c r="B63" t="s">
@@ -15303,7 +15423,7 @@
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A64" s="3" t="s">
+      <c r="A64" t="s">
         <v>4551</v>
       </c>
       <c r="B64" t="s">
@@ -15317,7 +15437,7 @@
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A65" s="3" t="s">
+      <c r="A65" t="s">
         <v>152</v>
       </c>
       <c r="B65" t="s">
@@ -15331,7 +15451,7 @@
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A66" s="3" t="s">
+      <c r="A66" t="s">
         <v>155</v>
       </c>
       <c r="B66" t="s">
@@ -15345,7 +15465,7 @@
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A67" s="3" t="s">
+      <c r="A67" t="s">
         <v>157</v>
       </c>
       <c r="B67" t="s">
@@ -15359,7 +15479,7 @@
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A68" s="3" t="s">
+      <c r="A68" t="s">
         <v>4552</v>
       </c>
       <c r="B68" t="s">
@@ -15373,7 +15493,7 @@
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A69" s="3" t="s">
+      <c r="A69" t="s">
         <v>160</v>
       </c>
       <c r="B69" t="s">
@@ -15387,7 +15507,7 @@
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A70" s="3" t="s">
+      <c r="A70" t="s">
         <v>162</v>
       </c>
       <c r="B70" t="s">
@@ -15401,7 +15521,7 @@
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A71" s="3" t="s">
+      <c r="A71" t="s">
         <v>164</v>
       </c>
       <c r="B71" t="s">
@@ -15415,7 +15535,7 @@
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A72" s="3" t="s">
+      <c r="A72" t="s">
         <v>4553</v>
       </c>
       <c r="B72" t="s">
@@ -15429,7 +15549,7 @@
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A73" s="3" t="s">
+      <c r="A73" t="s">
         <v>167</v>
       </c>
       <c r="B73" t="s">
@@ -15443,7 +15563,7 @@
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A74" s="3" t="s">
+      <c r="A74" t="s">
         <v>169</v>
       </c>
       <c r="B74" t="s">
@@ -15457,7 +15577,7 @@
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A75" s="3" t="s">
+      <c r="A75" t="s">
         <v>172</v>
       </c>
       <c r="B75" t="s">
@@ -15471,7 +15591,7 @@
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A76" s="3" t="s">
+      <c r="A76" t="s">
         <v>4554</v>
       </c>
       <c r="B76" t="s">
@@ -15485,7 +15605,7 @@
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A77" s="3" t="s">
+      <c r="A77" t="s">
         <v>176</v>
       </c>
       <c r="B77" t="s">
@@ -15499,7 +15619,7 @@
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A78" s="3" t="s">
+      <c r="A78" t="s">
         <v>179</v>
       </c>
       <c r="B78" t="s">
@@ -15513,7 +15633,7 @@
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A79" s="3" t="s">
+      <c r="A79" t="s">
         <v>182</v>
       </c>
       <c r="B79" t="s">
@@ -15527,7 +15647,7 @@
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A80" s="3" t="s">
+      <c r="A80" t="s">
         <v>4555</v>
       </c>
       <c r="B80" t="s">
@@ -15541,7 +15661,7 @@
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A81" s="3" t="s">
+      <c r="A81" t="s">
         <v>186</v>
       </c>
       <c r="B81" t="s">
@@ -15555,7 +15675,7 @@
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A82" s="3" t="s">
+      <c r="A82" t="s">
         <v>189</v>
       </c>
       <c r="B82" t="s">
@@ -15569,7 +15689,7 @@
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A83" s="3" t="s">
+      <c r="A83" t="s">
         <v>192</v>
       </c>
       <c r="B83" t="s">
@@ -15583,7 +15703,7 @@
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A84" s="3" t="s">
+      <c r="A84" t="s">
         <v>4556</v>
       </c>
       <c r="B84" t="s">
@@ -15597,7 +15717,7 @@
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A85" s="3" t="s">
+      <c r="A85" t="s">
         <v>196</v>
       </c>
       <c r="B85" t="s">
@@ -15611,7 +15731,7 @@
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A86" s="3" t="s">
+      <c r="A86" t="s">
         <v>199</v>
       </c>
       <c r="B86" t="s">
@@ -15625,7 +15745,7 @@
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A87" s="3" t="s">
+      <c r="A87" t="s">
         <v>202</v>
       </c>
       <c r="B87" t="s">
@@ -15639,7 +15759,7 @@
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A88" s="3" t="s">
+      <c r="A88" t="s">
         <v>4557</v>
       </c>
       <c r="B88" t="s">
@@ -15653,7 +15773,7 @@
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A89" s="3" t="s">
+      <c r="A89" t="s">
         <v>206</v>
       </c>
       <c r="B89" t="s">
@@ -15667,7 +15787,7 @@
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A90" s="3" t="s">
+      <c r="A90" t="s">
         <v>209</v>
       </c>
       <c r="B90" t="s">
@@ -15681,7 +15801,7 @@
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A91" s="3" t="s">
+      <c r="A91" t="s">
         <v>212</v>
       </c>
       <c r="B91" t="s">
@@ -15695,7 +15815,7 @@
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A92" s="3" t="s">
+      <c r="A92" t="s">
         <v>4558</v>
       </c>
       <c r="B92" t="s">
@@ -15709,7 +15829,7 @@
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A93" s="3" t="s">
+      <c r="A93" t="s">
         <v>216</v>
       </c>
       <c r="B93" t="s">
@@ -15723,7 +15843,7 @@
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A94" s="3" t="s">
+      <c r="A94" t="s">
         <v>219</v>
       </c>
       <c r="B94" t="s">
@@ -15737,7 +15857,7 @@
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A95" s="3" t="s">
+      <c r="A95" t="s">
         <v>222</v>
       </c>
       <c r="B95" t="s">
@@ -15751,7 +15871,7 @@
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A96" s="3" t="s">
+      <c r="A96" t="s">
         <v>4559</v>
       </c>
       <c r="B96" t="s">
@@ -15765,7 +15885,7 @@
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A97" s="3" t="s">
+      <c r="A97" t="s">
         <v>226</v>
       </c>
       <c r="B97" t="s">
@@ -15779,7 +15899,7 @@
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A98" s="3" t="s">
+      <c r="A98" t="s">
         <v>4560</v>
       </c>
       <c r="B98" t="s">
@@ -15793,7 +15913,7 @@
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A99" s="3" t="s">
+      <c r="A99" t="s">
         <v>4561</v>
       </c>
       <c r="B99" t="s">
@@ -15807,7 +15927,7 @@
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A100" s="3" t="s">
+      <c r="A100" t="s">
         <v>4562</v>
       </c>
       <c r="B100" t="s">
@@ -15821,7 +15941,7 @@
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A101" s="3" t="s">
+      <c r="A101" t="s">
         <v>4563</v>
       </c>
       <c r="B101" t="s">
@@ -15835,7 +15955,7 @@
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A102" s="3" t="s">
+      <c r="A102" t="s">
         <v>4564</v>
       </c>
       <c r="B102" t="s">
@@ -15849,7 +15969,7 @@
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A103" s="3" t="s">
+      <c r="A103" t="s">
         <v>4565</v>
       </c>
       <c r="B103" t="s">
@@ -15863,7 +15983,7 @@
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A104" s="3" t="s">
+      <c r="A104" t="s">
         <v>4566</v>
       </c>
       <c r="B104" t="s">
@@ -15877,7 +15997,7 @@
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A105" s="3" t="s">
+      <c r="A105" t="s">
         <v>4567</v>
       </c>
       <c r="B105" t="s">
@@ -15891,7 +16011,7 @@
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A106" s="3" t="s">
+      <c r="A106" t="s">
         <v>4568</v>
       </c>
       <c r="B106" t="s">
@@ -15905,7 +16025,7 @@
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A107" s="3" t="s">
+      <c r="A107" t="s">
         <v>4569</v>
       </c>
       <c r="B107" t="s">
@@ -15919,7 +16039,7 @@
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A108" s="3" t="s">
+      <c r="A108" t="s">
         <v>4570</v>
       </c>
       <c r="B108" t="s">
@@ -15933,7 +16053,7 @@
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A109" s="3" t="s">
+      <c r="A109" t="s">
         <v>4571</v>
       </c>
       <c r="B109" t="s">
@@ -15947,7 +16067,7 @@
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A110" s="3" t="s">
+      <c r="A110" t="s">
         <v>229</v>
       </c>
       <c r="B110" t="s">
@@ -15961,7 +16081,7 @@
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A111" s="3" t="s">
+      <c r="A111" t="s">
         <v>232</v>
       </c>
       <c r="B111" t="s">
@@ -15975,7 +16095,7 @@
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A112" s="3" t="s">
+      <c r="A112" t="s">
         <v>4572</v>
       </c>
       <c r="B112" t="s">
@@ -15989,7 +16109,7 @@
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A113" s="3" t="s">
+      <c r="A113" t="s">
         <v>236</v>
       </c>
       <c r="B113" t="s">
@@ -16003,7 +16123,7 @@
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A114" s="3" t="s">
+      <c r="A114" t="s">
         <v>239</v>
       </c>
       <c r="B114" t="s">
@@ -16017,7 +16137,7 @@
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A115" s="3" t="s">
+      <c r="A115" t="s">
         <v>242</v>
       </c>
       <c r="B115" t="s">
@@ -16031,7 +16151,7 @@
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A116" s="3" t="s">
+      <c r="A116" t="s">
         <v>4573</v>
       </c>
       <c r="B116" t="s">
@@ -16045,7 +16165,7 @@
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A117" s="3" t="s">
+      <c r="A117" t="s">
         <v>246</v>
       </c>
       <c r="B117" t="s">
@@ -16059,7 +16179,7 @@
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A118" s="3" t="s">
+      <c r="A118" t="s">
         <v>249</v>
       </c>
       <c r="B118" t="s">
@@ -16073,7 +16193,7 @@
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A119" s="3" t="s">
+      <c r="A119" t="s">
         <v>252</v>
       </c>
       <c r="B119" t="s">
@@ -16087,7 +16207,7 @@
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A120" s="3" t="s">
+      <c r="A120" t="s">
         <v>4574</v>
       </c>
       <c r="B120" t="s">
@@ -16101,7 +16221,7 @@
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A121" s="3" t="s">
+      <c r="A121" t="s">
         <v>256</v>
       </c>
       <c r="B121" t="s">
@@ -16115,7 +16235,7 @@
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A122" s="3" t="s">
+      <c r="A122" t="s">
         <v>259</v>
       </c>
       <c r="B122" t="s">
@@ -16129,7 +16249,7 @@
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A123" s="3" t="s">
+      <c r="A123" t="s">
         <v>262</v>
       </c>
       <c r="B123" t="s">
@@ -16143,7 +16263,7 @@
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A124" s="3" t="s">
+      <c r="A124" t="s">
         <v>4575</v>
       </c>
       <c r="B124" t="s">
@@ -16157,7 +16277,7 @@
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A125" s="3" t="s">
+      <c r="A125" t="s">
         <v>266</v>
       </c>
       <c r="B125" t="s">
@@ -16171,7 +16291,7 @@
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A126" s="3" t="s">
+      <c r="A126" t="s">
         <v>269</v>
       </c>
       <c r="B126" t="s">
@@ -16185,7 +16305,7 @@
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A127" s="3" t="s">
+      <c r="A127" t="s">
         <v>272</v>
       </c>
       <c r="B127" t="s">
@@ -16199,7 +16319,7 @@
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A128" s="3" t="s">
+      <c r="A128" t="s">
         <v>4576</v>
       </c>
       <c r="B128" t="s">
@@ -16213,7 +16333,7 @@
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A129" s="3" t="s">
+      <c r="A129" t="s">
         <v>276</v>
       </c>
       <c r="B129" t="s">
@@ -16227,7 +16347,7 @@
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A130" s="3" t="s">
+      <c r="A130" t="s">
         <v>279</v>
       </c>
       <c r="B130" t="s">
@@ -16241,7 +16361,7 @@
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A131" s="3" t="s">
+      <c r="A131" t="s">
         <v>282</v>
       </c>
       <c r="B131" t="s">
@@ -16255,7 +16375,7 @@
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A132" s="3" t="s">
+      <c r="A132" t="s">
         <v>4577</v>
       </c>
       <c r="B132" t="s">
@@ -16269,7 +16389,7 @@
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A133" s="3" t="s">
+      <c r="A133" t="s">
         <v>286</v>
       </c>
       <c r="B133" t="s">
@@ -16283,7 +16403,7 @@
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A134" s="3" t="s">
+      <c r="A134" t="s">
         <v>289</v>
       </c>
       <c r="B134" t="s">
@@ -16297,7 +16417,7 @@
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A135" s="3" t="s">
+      <c r="A135" t="s">
         <v>292</v>
       </c>
       <c r="B135" t="s">
@@ -16311,7 +16431,7 @@
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A136" s="3" t="s">
+      <c r="A136" t="s">
         <v>4578</v>
       </c>
       <c r="B136" t="s">
@@ -16325,7 +16445,7 @@
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A137" s="3" t="s">
+      <c r="A137" t="s">
         <v>296</v>
       </c>
       <c r="B137" t="s">
@@ -16339,7 +16459,7 @@
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A138" s="3" t="s">
+      <c r="A138" t="s">
         <v>299</v>
       </c>
       <c r="B138" t="s">
@@ -16353,7 +16473,7 @@
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A139" s="3" t="s">
+      <c r="A139" t="s">
         <v>302</v>
       </c>
       <c r="B139" t="s">
@@ -16367,7 +16487,7 @@
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A140" s="3" t="s">
+      <c r="A140" t="s">
         <v>4579</v>
       </c>
       <c r="B140" t="s">
@@ -16381,7 +16501,7 @@
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A141" s="3" t="s">
+      <c r="A141" t="s">
         <v>306</v>
       </c>
       <c r="B141" t="s">
@@ -16395,7 +16515,7 @@
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A142" s="3" t="s">
+      <c r="A142" t="s">
         <v>309</v>
       </c>
       <c r="B142" t="s">
@@ -16409,7 +16529,7 @@
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A143" s="3" t="s">
+      <c r="A143" t="s">
         <v>312</v>
       </c>
       <c r="B143" t="s">
@@ -16423,7 +16543,7 @@
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A144" s="3" t="s">
+      <c r="A144" t="s">
         <v>4580</v>
       </c>
       <c r="B144" t="s">
@@ -16437,7 +16557,7 @@
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A145" s="3" t="s">
+      <c r="A145" t="s">
         <v>316</v>
       </c>
       <c r="B145" t="s">
@@ -16451,7 +16571,7 @@
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A146" s="3" t="s">
+      <c r="A146" t="s">
         <v>4581</v>
       </c>
       <c r="B146" t="s">
@@ -16465,7 +16585,7 @@
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A147" s="3" t="s">
+      <c r="A147" t="s">
         <v>4582</v>
       </c>
       <c r="B147" t="s">
@@ -16479,7 +16599,7 @@
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A148" s="3" t="s">
+      <c r="A148" t="s">
         <v>4583</v>
       </c>
       <c r="B148" t="s">
@@ -16493,7 +16613,7 @@
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A149" s="3" t="s">
+      <c r="A149" t="s">
         <v>4584</v>
       </c>
       <c r="B149" t="s">
@@ -16507,7 +16627,7 @@
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A150" s="3" t="s">
+      <c r="A150" t="s">
         <v>4585</v>
       </c>
       <c r="B150" t="s">
@@ -16521,7 +16641,7 @@
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A151" s="3" t="s">
+      <c r="A151" t="s">
         <v>4586</v>
       </c>
       <c r="B151" t="s">
@@ -16535,7 +16655,7 @@
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A152" s="3" t="s">
+      <c r="A152" t="s">
         <v>4587</v>
       </c>
       <c r="B152" t="s">
@@ -16549,7 +16669,7 @@
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A153" s="3" t="s">
+      <c r="A153" t="s">
         <v>4588</v>
       </c>
       <c r="B153" t="s">
@@ -16563,7 +16683,7 @@
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A154" s="3" t="s">
+      <c r="A154" t="s">
         <v>4589</v>
       </c>
       <c r="B154" t="s">
@@ -16577,7 +16697,7 @@
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A155" s="3" t="s">
+      <c r="A155" t="s">
         <v>4590</v>
       </c>
       <c r="B155" t="s">
@@ -16591,7 +16711,7 @@
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A156" s="3" t="s">
+      <c r="A156" t="s">
         <v>4591</v>
       </c>
       <c r="B156" t="s">
@@ -16605,7 +16725,7 @@
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A157" s="3" t="s">
+      <c r="A157" t="s">
         <v>4592</v>
       </c>
       <c r="B157" t="s">
@@ -16619,63 +16739,63 @@
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A158" s="3" t="s">
+      <c r="A158" t="s">
         <v>4593</v>
       </c>
       <c r="B158" t="s">
         <v>334</v>
       </c>
       <c r="C158" t="s">
-        <v>335</v>
+        <v>4636</v>
       </c>
       <c r="D158" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A159" s="3" t="s">
+      <c r="A159" t="s">
         <v>4594</v>
       </c>
       <c r="B159" t="s">
         <v>336</v>
       </c>
       <c r="C159" t="s">
-        <v>337</v>
+        <v>4637</v>
       </c>
       <c r="D159" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A160" s="3" t="s">
+      <c r="A160" t="s">
         <v>4595</v>
       </c>
       <c r="B160" t="s">
         <v>338</v>
       </c>
       <c r="C160" t="s">
-        <v>906</v>
+        <v>4638</v>
       </c>
       <c r="D160" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A161" s="3" t="s">
+      <c r="A161" t="s">
         <v>4596</v>
       </c>
       <c r="B161" t="s">
         <v>339</v>
       </c>
       <c r="C161" t="s">
-        <v>340</v>
+        <v>4639</v>
       </c>
       <c r="D161" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A162" s="3" t="s">
+      <c r="A162" t="s">
         <v>4597</v>
       </c>
       <c r="B162" t="s">
@@ -16689,7 +16809,7 @@
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A163" s="3" t="s">
+      <c r="A163" t="s">
         <v>4598</v>
       </c>
       <c r="B163" t="s">
@@ -16703,7 +16823,7 @@
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A164" s="3" t="s">
+      <c r="A164" t="s">
         <v>4599</v>
       </c>
       <c r="B164" t="s">
@@ -16717,7 +16837,7 @@
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A165" s="3" t="s">
+      <c r="A165" t="s">
         <v>4600</v>
       </c>
       <c r="B165" t="s">
@@ -16731,7 +16851,7 @@
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A166" s="3" t="s">
+      <c r="A166" t="s">
         <v>4601</v>
       </c>
       <c r="B166" t="s">
@@ -16745,7 +16865,7 @@
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A167" s="3" t="s">
+      <c r="A167" t="s">
         <v>4602</v>
       </c>
       <c r="B167" t="s">
@@ -16759,7 +16879,7 @@
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A168" s="3" t="s">
+      <c r="A168" t="s">
         <v>4603</v>
       </c>
       <c r="B168" t="s">
@@ -16773,7 +16893,7 @@
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A169" s="3" t="s">
+      <c r="A169" t="s">
         <v>4604</v>
       </c>
       <c r="B169" t="s">
@@ -16787,7 +16907,7 @@
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A170" s="3" t="s">
+      <c r="A170" t="s">
         <v>4605</v>
       </c>
       <c r="B170" t="s">
@@ -16801,7 +16921,7 @@
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A171" s="3" t="s">
+      <c r="A171" t="s">
         <v>4606</v>
       </c>
       <c r="B171" t="s">
@@ -16815,7 +16935,7 @@
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A172" s="3" t="s">
+      <c r="A172" t="s">
         <v>4607</v>
       </c>
       <c r="B172" t="s">
@@ -16829,7 +16949,7 @@
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A173" s="3" t="s">
+      <c r="A173" t="s">
         <v>4608</v>
       </c>
       <c r="B173" t="s">
@@ -16843,7 +16963,7 @@
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A174" s="3" t="s">
+      <c r="A174" t="s">
         <v>4609</v>
       </c>
       <c r="B174" t="s">
@@ -16857,7 +16977,7 @@
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A175" s="3" t="s">
+      <c r="A175" t="s">
         <v>4610</v>
       </c>
       <c r="B175" t="s">
@@ -16871,7 +16991,7 @@
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A176" s="3" t="s">
+      <c r="A176" t="s">
         <v>4611</v>
       </c>
       <c r="B176" t="s">
@@ -16885,7 +17005,7 @@
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A177" s="3" t="s">
+      <c r="A177" t="s">
         <v>4612</v>
       </c>
       <c r="B177" t="s">
@@ -16899,175 +17019,175 @@
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A178" s="3" t="s">
+      <c r="A178" t="s">
         <v>366</v>
       </c>
       <c r="B178" t="s">
         <v>367</v>
       </c>
       <c r="C178" t="s">
-        <v>4636</v>
+        <v>4640</v>
       </c>
       <c r="D178" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A179" s="3" t="s">
+      <c r="A179" t="s">
         <v>368</v>
       </c>
       <c r="B179" t="s">
         <v>369</v>
       </c>
       <c r="C179" t="s">
-        <v>4637</v>
+        <v>4641</v>
       </c>
       <c r="D179" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A180" s="3" t="s">
+      <c r="A180" t="s">
         <v>4613</v>
       </c>
       <c r="B180" t="s">
         <v>370</v>
       </c>
       <c r="C180" t="s">
-        <v>4638</v>
+        <v>4642</v>
       </c>
       <c r="D180" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A181" s="3" t="s">
+      <c r="A181" t="s">
         <v>371</v>
       </c>
       <c r="B181" t="s">
         <v>372</v>
       </c>
       <c r="C181" t="s">
-        <v>4639</v>
+        <v>4643</v>
       </c>
       <c r="D181" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A182" s="3" t="s">
+      <c r="A182" t="s">
         <v>373</v>
       </c>
       <c r="B182" t="s">
         <v>379</v>
       </c>
       <c r="C182" t="s">
-        <v>4640</v>
+        <v>4644</v>
       </c>
       <c r="D182" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A183" s="3" t="s">
+      <c r="A183" t="s">
         <v>374</v>
       </c>
       <c r="B183" t="s">
         <v>380</v>
       </c>
       <c r="C183" t="s">
-        <v>4641</v>
+        <v>4645</v>
       </c>
       <c r="D183" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A184" s="3" t="s">
+      <c r="A184" t="s">
         <v>4614</v>
       </c>
       <c r="B184" t="s">
         <v>381</v>
       </c>
       <c r="C184" t="s">
-        <v>4642</v>
+        <v>4646</v>
       </c>
       <c r="D184" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A185" s="3" t="s">
+      <c r="A185" t="s">
         <v>375</v>
       </c>
       <c r="B185" t="s">
         <v>382</v>
       </c>
       <c r="C185" t="s">
-        <v>4643</v>
+        <v>4647</v>
       </c>
       <c r="D185" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A186" s="3" t="s">
+      <c r="A186" t="s">
         <v>376</v>
       </c>
       <c r="B186" t="s">
         <v>383</v>
       </c>
       <c r="C186" t="s">
-        <v>4644</v>
+        <v>4648</v>
       </c>
       <c r="D186" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A187" s="3" t="s">
+      <c r="A187" t="s">
         <v>377</v>
       </c>
       <c r="B187" t="s">
         <v>384</v>
       </c>
       <c r="C187" t="s">
-        <v>4645</v>
+        <v>4649</v>
       </c>
       <c r="D187" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A188" s="3" t="s">
+      <c r="A188" t="s">
         <v>4615</v>
       </c>
       <c r="B188" t="s">
         <v>385</v>
       </c>
       <c r="C188" t="s">
-        <v>4646</v>
+        <v>4650</v>
       </c>
       <c r="D188" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A189" s="3" t="s">
+      <c r="A189" t="s">
         <v>378</v>
       </c>
       <c r="B189" t="s">
         <v>386</v>
       </c>
       <c r="C189" t="s">
-        <v>4647</v>
+        <v>4651</v>
       </c>
       <c r="D189" t="s">
         <v>10</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="B2:D189">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D189">
     <sortCondition ref="B2:B189"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -17100,7 +17220,7 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" t="s">
         <v>387</v>
       </c>
       <c r="B2" t="s">
@@ -17114,7 +17234,7 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" t="s">
         <v>390</v>
       </c>
       <c r="B3" t="s">
@@ -17128,7 +17248,7 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+      <c r="A4" t="s">
         <v>4484</v>
       </c>
       <c r="B4" t="s">
@@ -17142,7 +17262,7 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+      <c r="A5" t="s">
         <v>394</v>
       </c>
       <c r="B5" t="s">
@@ -17156,7 +17276,7 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
+      <c r="A6" t="s">
         <v>397</v>
       </c>
       <c r="B6" t="s">
@@ -17170,7 +17290,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
+      <c r="A7" t="s">
         <v>400</v>
       </c>
       <c r="B7" t="s">
@@ -17184,7 +17304,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
+      <c r="A8" t="s">
         <v>4485</v>
       </c>
       <c r="B8" t="s">
@@ -17198,7 +17318,7 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
+      <c r="A9" t="s">
         <v>404</v>
       </c>
       <c r="B9" t="s">
@@ -17212,7 +17332,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
+      <c r="A10" t="s">
         <v>407</v>
       </c>
       <c r="B10" t="s">
@@ -17226,7 +17346,7 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
+      <c r="A11" t="s">
         <v>410</v>
       </c>
       <c r="B11" t="s">
@@ -17240,7 +17360,7 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
+      <c r="A12" t="s">
         <v>4486</v>
       </c>
       <c r="B12" t="s">
@@ -17254,7 +17374,7 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
+      <c r="A13" t="s">
         <v>414</v>
       </c>
       <c r="B13" t="s">
@@ -17268,7 +17388,7 @@
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
+      <c r="A14" t="s">
         <v>417</v>
       </c>
       <c r="B14" t="s">
@@ -17282,7 +17402,7 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
+      <c r="A15" t="s">
         <v>420</v>
       </c>
       <c r="B15" t="s">
@@ -17296,7 +17416,7 @@
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
+      <c r="A16" t="s">
         <v>4487</v>
       </c>
       <c r="B16" t="s">
@@ -17310,7 +17430,7 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
+      <c r="A17" t="s">
         <v>424</v>
       </c>
       <c r="B17" t="s">
@@ -17324,7 +17444,7 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
+      <c r="A18" t="s">
         <v>427</v>
       </c>
       <c r="B18" t="s">
@@ -17338,7 +17458,7 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
+      <c r="A19" t="s">
         <v>430</v>
       </c>
       <c r="B19" t="s">
@@ -17352,7 +17472,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="s">
+      <c r="A20" t="s">
         <v>4488</v>
       </c>
       <c r="B20" t="s">
@@ -17366,7 +17486,7 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="3" t="s">
+      <c r="A21" t="s">
         <v>434</v>
       </c>
       <c r="B21" t="s">
@@ -17380,7 +17500,7 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="3" t="s">
+      <c r="A22" t="s">
         <v>437</v>
       </c>
       <c r="B22" t="s">
@@ -17394,7 +17514,7 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="3" t="s">
+      <c r="A23" t="s">
         <v>440</v>
       </c>
       <c r="B23" t="s">
@@ -17408,7 +17528,7 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="3" t="s">
+      <c r="A24" t="s">
         <v>4489</v>
       </c>
       <c r="B24" t="s">
@@ -17422,7 +17542,7 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="3" t="s">
+      <c r="A25" t="s">
         <v>444</v>
       </c>
       <c r="B25" t="s">
@@ -17436,7 +17556,7 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="3" t="s">
+      <c r="A26" t="s">
         <v>447</v>
       </c>
       <c r="B26" t="s">
@@ -17450,7 +17570,7 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="3" t="s">
+      <c r="A27" t="s">
         <v>450</v>
       </c>
       <c r="B27" t="s">
@@ -17464,7 +17584,7 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="3" t="s">
+      <c r="A28" t="s">
         <v>4490</v>
       </c>
       <c r="B28" t="s">
@@ -17478,7 +17598,7 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="3" t="s">
+      <c r="A29" t="s">
         <v>454</v>
       </c>
       <c r="B29" t="s">
@@ -17492,7 +17612,7 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="3" t="s">
+      <c r="A30" t="s">
         <v>457</v>
       </c>
       <c r="B30" t="s">
@@ -17506,7 +17626,7 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="3" t="s">
+      <c r="A31" t="s">
         <v>460</v>
       </c>
       <c r="B31" t="s">
@@ -17520,7 +17640,7 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="3" t="s">
+      <c r="A32" t="s">
         <v>4491</v>
       </c>
       <c r="B32" t="s">
@@ -17534,7 +17654,7 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="3" t="s">
+      <c r="A33" t="s">
         <v>464</v>
       </c>
       <c r="B33" t="s">
@@ -17548,7 +17668,7 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="3" t="s">
+      <c r="A34" t="s">
         <v>467</v>
       </c>
       <c r="B34" t="s">
@@ -17562,7 +17682,7 @@
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="3" t="s">
+      <c r="A35" t="s">
         <v>470</v>
       </c>
       <c r="B35" t="s">
@@ -17576,7 +17696,7 @@
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="3" t="s">
+      <c r="A36" t="s">
         <v>4492</v>
       </c>
       <c r="B36" t="s">
@@ -17590,7 +17710,7 @@
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="3" t="s">
+      <c r="A37" t="s">
         <v>474</v>
       </c>
       <c r="B37" t="s">
@@ -17604,7 +17724,7 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="3" t="s">
+      <c r="A38" t="s">
         <v>4493</v>
       </c>
       <c r="B38" t="s">
@@ -17618,7 +17738,7 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="3" t="s">
+      <c r="A39" t="s">
         <v>4494</v>
       </c>
       <c r="B39" t="s">
@@ -17632,7 +17752,7 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="3" t="s">
+      <c r="A40" t="s">
         <v>4495</v>
       </c>
       <c r="B40" t="s">
@@ -17646,7 +17766,7 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" s="3" t="s">
+      <c r="A41" t="s">
         <v>4496</v>
       </c>
       <c r="B41" t="s">
@@ -17660,7 +17780,7 @@
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" s="3" t="s">
+      <c r="A42" t="s">
         <v>477</v>
       </c>
       <c r="B42" t="s">
@@ -17674,7 +17794,7 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" s="3" t="s">
+      <c r="A43" t="s">
         <v>480</v>
       </c>
       <c r="B43" t="s">
@@ -17688,7 +17808,7 @@
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" s="3" t="s">
+      <c r="A44" t="s">
         <v>4497</v>
       </c>
       <c r="B44" t="s">
@@ -17702,7 +17822,7 @@
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" s="3" t="s">
+      <c r="A45" t="s">
         <v>484</v>
       </c>
       <c r="B45" t="s">
@@ -17716,7 +17836,7 @@
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46" s="3" t="s">
+      <c r="A46" t="s">
         <v>487</v>
       </c>
       <c r="B46" t="s">
@@ -17730,7 +17850,7 @@
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47" s="3" t="s">
+      <c r="A47" t="s">
         <v>488</v>
       </c>
       <c r="B47" t="s">
@@ -17744,7 +17864,7 @@
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" s="3" t="s">
+      <c r="A48" t="s">
         <v>4498</v>
       </c>
       <c r="B48" t="s">
@@ -17758,7 +17878,7 @@
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A49" s="3" t="s">
+      <c r="A49" t="s">
         <v>489</v>
       </c>
       <c r="B49" t="s">
@@ -17772,7 +17892,7 @@
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A50" s="3" t="s">
+      <c r="A50" t="s">
         <v>497</v>
       </c>
       <c r="B50" t="s">
@@ -17786,7 +17906,7 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A51" s="3" t="s">
+      <c r="A51" t="s">
         <v>500</v>
       </c>
       <c r="B51" t="s">
@@ -17800,7 +17920,7 @@
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A52" s="3" t="s">
+      <c r="A52" t="s">
         <v>4499</v>
       </c>
       <c r="B52" t="s">
@@ -17814,7 +17934,7 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A53" s="3" t="s">
+      <c r="A53" t="s">
         <v>504</v>
       </c>
       <c r="B53" t="s">
@@ -17828,7 +17948,7 @@
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A54" s="3" t="s">
+      <c r="A54" t="s">
         <v>507</v>
       </c>
       <c r="B54" t="s">
@@ -17842,7 +17962,7 @@
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A55" s="3" t="s">
+      <c r="A55" t="s">
         <v>510</v>
       </c>
       <c r="B55" t="s">
@@ -17856,7 +17976,7 @@
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A56" s="3" t="s">
+      <c r="A56" t="s">
         <v>4500</v>
       </c>
       <c r="B56" t="s">
@@ -17870,7 +17990,7 @@
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A57" s="3" t="s">
+      <c r="A57" t="s">
         <v>514</v>
       </c>
       <c r="B57" t="s">
@@ -17884,7 +18004,7 @@
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58" s="3" t="s">
+      <c r="A58" t="s">
         <v>517</v>
       </c>
       <c r="B58" t="s">
@@ -17898,7 +18018,7 @@
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A59" s="3" t="s">
+      <c r="A59" t="s">
         <v>520</v>
       </c>
       <c r="B59" t="s">
@@ -17912,7 +18032,7 @@
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A60" s="3" t="s">
+      <c r="A60" t="s">
         <v>4501</v>
       </c>
       <c r="B60" t="s">
@@ -17926,7 +18046,7 @@
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A61" s="3" t="s">
+      <c r="A61" t="s">
         <v>524</v>
       </c>
       <c r="B61" t="s">
@@ -17940,7 +18060,7 @@
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A62" s="3" t="s">
+      <c r="A62" t="s">
         <v>527</v>
       </c>
       <c r="B62" t="s">
@@ -17954,7 +18074,7 @@
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A63" s="3" t="s">
+      <c r="A63" t="s">
         <v>528</v>
       </c>
       <c r="B63" t="s">
@@ -17968,7 +18088,7 @@
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A64" s="3" t="s">
+      <c r="A64" t="s">
         <v>4502</v>
       </c>
       <c r="B64" t="s">
@@ -17982,7 +18102,7 @@
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A65" s="3" t="s">
+      <c r="A65" t="s">
         <v>529</v>
       </c>
       <c r="B65" t="s">
@@ -17996,7 +18116,7 @@
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A66" s="3" t="s">
+      <c r="A66" t="s">
         <v>4503</v>
       </c>
       <c r="B66" t="s">
@@ -18010,7 +18130,7 @@
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A67" s="3" t="s">
+      <c r="A67" t="s">
         <v>4504</v>
       </c>
       <c r="B67" t="s">
@@ -18024,7 +18144,7 @@
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A68" s="3" t="s">
+      <c r="A68" t="s">
         <v>4505</v>
       </c>
       <c r="B68" t="s">
@@ -18038,7 +18158,7 @@
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A69" s="3" t="s">
+      <c r="A69" t="s">
         <v>4506</v>
       </c>
       <c r="B69" t="s">
@@ -18052,7 +18172,7 @@
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A70" s="3" t="s">
+      <c r="A70" t="s">
         <v>4507</v>
       </c>
       <c r="B70" t="s">
@@ -18066,7 +18186,7 @@
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A71" s="3" t="s">
+      <c r="A71" t="s">
         <v>4508</v>
       </c>
       <c r="B71" t="s">
@@ -18080,7 +18200,7 @@
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A72" s="3" t="s">
+      <c r="A72" t="s">
         <v>4509</v>
       </c>
       <c r="B72" t="s">
@@ -18094,7 +18214,7 @@
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A73" s="3" t="s">
+      <c r="A73" t="s">
         <v>4510</v>
       </c>
       <c r="B73" t="s">
@@ -18108,7 +18228,7 @@
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A74" s="3" t="s">
+      <c r="A74" t="s">
         <v>4511</v>
       </c>
       <c r="B74" t="s">
@@ -18122,7 +18242,7 @@
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A75" s="3" t="s">
+      <c r="A75" t="s">
         <v>4512</v>
       </c>
       <c r="B75" t="s">
@@ -18136,7 +18256,7 @@
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A76" s="3" t="s">
+      <c r="A76" t="s">
         <v>4513</v>
       </c>
       <c r="B76" t="s">
@@ -18150,7 +18270,7 @@
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A77" s="3" t="s">
+      <c r="A77" t="s">
         <v>4514</v>
       </c>
       <c r="B77" t="s">
@@ -18164,7 +18284,7 @@
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A78" s="3" t="s">
+      <c r="A78" t="s">
         <v>537</v>
       </c>
       <c r="B78" t="s">
@@ -18178,7 +18298,7 @@
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A79" s="3" t="s">
+      <c r="A79" t="s">
         <v>540</v>
       </c>
       <c r="B79" t="s">
@@ -18192,7 +18312,7 @@
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A80" s="3" t="s">
+      <c r="A80" t="s">
         <v>4515</v>
       </c>
       <c r="B80" t="s">
@@ -18206,7 +18326,7 @@
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A81" s="3" t="s">
+      <c r="A81" t="s">
         <v>544</v>
       </c>
       <c r="B81" t="s">
@@ -18220,7 +18340,7 @@
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A82" s="3" t="s">
+      <c r="A82" t="s">
         <v>547</v>
       </c>
       <c r="B82" t="s">
@@ -18234,7 +18354,7 @@
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A83" s="3" t="s">
+      <c r="A83" t="s">
         <v>550</v>
       </c>
       <c r="B83" t="s">
@@ -18248,7 +18368,7 @@
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A84" s="3" t="s">
+      <c r="A84" t="s">
         <v>4516</v>
       </c>
       <c r="B84" t="s">
@@ -18262,7 +18382,7 @@
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A85" s="3" t="s">
+      <c r="A85" t="s">
         <v>554</v>
       </c>
       <c r="B85" t="s">
@@ -18276,7 +18396,7 @@
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A86" s="3" t="s">
+      <c r="A86" t="s">
         <v>557</v>
       </c>
       <c r="B86" t="s">
@@ -18290,7 +18410,7 @@
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A87" s="3" t="s">
+      <c r="A87" t="s">
         <v>560</v>
       </c>
       <c r="B87" t="s">
@@ -18304,7 +18424,7 @@
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A88" s="3" t="s">
+      <c r="A88" t="s">
         <v>4517</v>
       </c>
       <c r="B88" t="s">
@@ -18318,7 +18438,7 @@
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A89" s="3" t="s">
+      <c r="A89" t="s">
         <v>564</v>
       </c>
       <c r="B89" t="s">
@@ -18331,330 +18451,330 @@
         <v>23</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
         <v>567</v>
       </c>
-      <c r="B90" t="s">
-        <v>568</v>
-      </c>
-      <c r="C90" t="s">
+      <c r="B90" s="3" t="s">
+        <v>4236</v>
+      </c>
+      <c r="C90" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="D90" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D90" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
         <v>570</v>
       </c>
-      <c r="B91" t="s">
-        <v>571</v>
-      </c>
-      <c r="C91" t="s">
+      <c r="B91" s="3" t="s">
+        <v>4238</v>
+      </c>
+      <c r="C91" s="3" t="s">
         <v>572</v>
       </c>
-      <c r="D91" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D91" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
         <v>4518</v>
       </c>
-      <c r="B92" t="s">
-        <v>573</v>
-      </c>
-      <c r="C92" t="s">
+      <c r="B92" s="3" t="s">
+        <v>4240</v>
+      </c>
+      <c r="C92" s="3" t="s">
         <v>931</v>
       </c>
-      <c r="D92" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D92" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
         <v>574</v>
       </c>
-      <c r="B93" t="s">
-        <v>575</v>
-      </c>
-      <c r="C93" t="s">
+      <c r="B93" s="3" t="s">
+        <v>4242</v>
+      </c>
+      <c r="C93" s="3" t="s">
         <v>576</v>
       </c>
-      <c r="D93" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D93" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
         <v>577</v>
       </c>
-      <c r="B94" t="s">
-        <v>578</v>
-      </c>
-      <c r="C94" t="s">
+      <c r="B94" s="3" t="s">
+        <v>4292</v>
+      </c>
+      <c r="C94" s="3" t="s">
         <v>579</v>
       </c>
-      <c r="D94" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D94" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
         <v>580</v>
       </c>
-      <c r="B95" t="s">
-        <v>581</v>
-      </c>
-      <c r="C95" t="s">
+      <c r="B95" s="3" t="s">
+        <v>4294</v>
+      </c>
+      <c r="C95" s="3" t="s">
         <v>582</v>
       </c>
-      <c r="D95" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D95" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
         <v>4519</v>
       </c>
-      <c r="B96" t="s">
-        <v>583</v>
-      </c>
-      <c r="C96" t="s">
+      <c r="B96" s="3" t="s">
+        <v>4296</v>
+      </c>
+      <c r="C96" s="3" t="s">
         <v>932</v>
       </c>
-      <c r="D96" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D96" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
         <v>584</v>
       </c>
-      <c r="B97" t="s">
-        <v>585</v>
-      </c>
-      <c r="C97" t="s">
+      <c r="B97" s="3" t="s">
+        <v>4298</v>
+      </c>
+      <c r="C97" s="3" t="s">
         <v>586</v>
       </c>
-      <c r="D97" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D97" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
         <v>587</v>
       </c>
-      <c r="B98" t="s">
-        <v>4252</v>
-      </c>
-      <c r="C98" t="s">
+      <c r="B98" s="3" t="s">
+        <v>4340</v>
+      </c>
+      <c r="C98" s="3" t="s">
         <v>589</v>
       </c>
-      <c r="D98" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D98" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
         <v>590</v>
       </c>
-      <c r="B99" t="s">
-        <v>4254</v>
-      </c>
-      <c r="C99" t="s">
+      <c r="B99" s="3" t="s">
+        <v>4342</v>
+      </c>
+      <c r="C99" s="3" t="s">
         <v>592</v>
       </c>
-      <c r="D99" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D99" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
         <v>4520</v>
       </c>
-      <c r="B100" t="s">
-        <v>4256</v>
-      </c>
-      <c r="C100" t="s">
+      <c r="B100" s="3" t="s">
+        <v>4344</v>
+      </c>
+      <c r="C100" s="3" t="s">
         <v>933</v>
       </c>
-      <c r="D100" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D100" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
         <v>594</v>
       </c>
-      <c r="B101" t="s">
-        <v>4258</v>
-      </c>
-      <c r="C101" t="s">
+      <c r="B101" s="3" t="s">
+        <v>4346</v>
+      </c>
+      <c r="C101" s="3" t="s">
         <v>596</v>
       </c>
-      <c r="D101" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D101" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A102" s="3" t="s">
         <v>597</v>
       </c>
-      <c r="B102" t="s">
-        <v>4308</v>
-      </c>
-      <c r="C102" t="s">
+      <c r="B102" s="3" t="s">
+        <v>4404</v>
+      </c>
+      <c r="C102" s="3" t="s">
         <v>599</v>
       </c>
-      <c r="D102" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D102" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
         <v>600</v>
       </c>
-      <c r="B103" t="s">
-        <v>4310</v>
-      </c>
-      <c r="C103" t="s">
+      <c r="B103" s="3" t="s">
+        <v>4406</v>
+      </c>
+      <c r="C103" s="3" t="s">
         <v>602</v>
       </c>
-      <c r="D103" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D103" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A104" s="3" t="s">
         <v>4521</v>
       </c>
-      <c r="B104" t="s">
-        <v>4312</v>
-      </c>
-      <c r="C104" t="s">
+      <c r="B104" s="3" t="s">
+        <v>4408</v>
+      </c>
+      <c r="C104" s="3" t="s">
         <v>934</v>
       </c>
-      <c r="D104" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D104" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A105" s="3" t="s">
         <v>604</v>
       </c>
-      <c r="B105" t="s">
-        <v>4314</v>
-      </c>
-      <c r="C105" t="s">
+      <c r="B105" s="3" t="s">
+        <v>4410</v>
+      </c>
+      <c r="C105" s="3" t="s">
         <v>606</v>
       </c>
-      <c r="D105" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D105" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
         <v>607</v>
       </c>
-      <c r="B106" t="s">
-        <v>4332</v>
-      </c>
-      <c r="C106" t="s">
+      <c r="B106" s="3" t="s">
+        <v>4428</v>
+      </c>
+      <c r="C106" s="3" t="s">
         <v>4620</v>
       </c>
-      <c r="D106" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D106" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
         <v>610</v>
       </c>
-      <c r="B107" t="s">
-        <v>4334</v>
-      </c>
-      <c r="C107" t="s">
+      <c r="B107" s="3" t="s">
+        <v>4430</v>
+      </c>
+      <c r="C107" s="3" t="s">
         <v>4621</v>
       </c>
-      <c r="D107" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D107" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A108" s="3" t="s">
         <v>4522</v>
       </c>
-      <c r="B108" t="s">
-        <v>4336</v>
-      </c>
-      <c r="C108" t="s">
+      <c r="B108" s="3" t="s">
+        <v>4432</v>
+      </c>
+      <c r="C108" s="3" t="s">
         <v>4622</v>
       </c>
-      <c r="D108" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D108" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
         <v>614</v>
       </c>
-      <c r="B109" t="s">
-        <v>4338</v>
-      </c>
-      <c r="C109" t="s">
+      <c r="B109" s="3" t="s">
+        <v>4434</v>
+      </c>
+      <c r="C109" s="3" t="s">
         <v>4623</v>
       </c>
-      <c r="D109" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D109" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A110" s="3" t="s">
         <v>617</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B110" s="3" t="s">
         <v>4200</v>
       </c>
-      <c r="C110" t="s">
+      <c r="C110" s="3" t="s">
         <v>4628</v>
       </c>
-      <c r="D110" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D110" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
         <v>620</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B111" s="3" t="s">
         <v>4201</v>
       </c>
-      <c r="C111" t="s">
+      <c r="C111" s="3" t="s">
         <v>4629</v>
       </c>
-      <c r="D111" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D111" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A112" s="3" t="s">
         <v>4523</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B112" s="3" t="s">
         <v>4202</v>
       </c>
-      <c r="C112" t="s">
+      <c r="C112" s="3" t="s">
         <v>4630</v>
       </c>
-      <c r="D112" t="s">
+      <c r="D112" s="3" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A113" s="3" t="s">
+      <c r="A113" t="s">
         <v>624</v>
       </c>
       <c r="B113" t="s">
@@ -18667,614 +18787,614 @@
         <v>23</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A114" s="3" t="s">
         <v>627</v>
       </c>
-      <c r="B114" t="s">
-        <v>4436</v>
-      </c>
-      <c r="C114" t="s">
+      <c r="B114" s="3" t="s">
+        <v>4476</v>
+      </c>
+      <c r="C114" s="3" t="s">
         <v>629</v>
       </c>
-      <c r="D114" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D114" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
         <v>630</v>
       </c>
-      <c r="B115" t="s">
-        <v>4438</v>
-      </c>
-      <c r="C115" t="s">
+      <c r="B115" s="3" t="s">
+        <v>4478</v>
+      </c>
+      <c r="C115" s="3" t="s">
         <v>632</v>
       </c>
-      <c r="D115" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D115" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A116" s="3" t="s">
         <v>4524</v>
       </c>
-      <c r="B116" t="s">
-        <v>4440</v>
-      </c>
-      <c r="C116" t="s">
+      <c r="B116" s="3" t="s">
+        <v>4480</v>
+      </c>
+      <c r="C116" s="3" t="s">
         <v>937</v>
       </c>
-      <c r="D116" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D116" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A117" s="3" t="s">
         <v>634</v>
       </c>
-      <c r="B117" t="s">
-        <v>4442</v>
-      </c>
-      <c r="C117" t="s">
+      <c r="B117" s="3" t="s">
+        <v>4482</v>
+      </c>
+      <c r="C117" s="3" t="s">
         <v>636</v>
       </c>
-      <c r="D117" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D117" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A118" s="3" t="s">
         <v>637</v>
       </c>
-      <c r="B118" t="s">
-        <v>648</v>
-      </c>
-      <c r="C118" t="s">
+      <c r="B118" s="3" t="s">
+        <v>4652</v>
+      </c>
+      <c r="C118" s="3" t="s">
         <v>639</v>
       </c>
-      <c r="D118" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D118" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
         <v>640</v>
       </c>
-      <c r="B119" t="s">
-        <v>651</v>
-      </c>
-      <c r="C119" t="s">
+      <c r="B119" s="3" t="s">
+        <v>4653</v>
+      </c>
+      <c r="C119" s="3" t="s">
         <v>642</v>
       </c>
-      <c r="D119" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D119" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A120" s="3" t="s">
         <v>4525</v>
       </c>
-      <c r="B120" t="s">
-        <v>653</v>
-      </c>
-      <c r="C120" t="s">
+      <c r="B120" s="3" t="s">
+        <v>4654</v>
+      </c>
+      <c r="C120" s="3" t="s">
         <v>938</v>
       </c>
-      <c r="D120" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D120" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A121" s="3" t="s">
         <v>644</v>
       </c>
-      <c r="B121" t="s">
-        <v>655</v>
-      </c>
-      <c r="C121" t="s">
+      <c r="B121" s="3" t="s">
+        <v>4655</v>
+      </c>
+      <c r="C121" s="3" t="s">
         <v>646</v>
       </c>
-      <c r="D121" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D121" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A122" s="3" t="s">
         <v>647</v>
       </c>
-      <c r="B122" t="s">
-        <v>698</v>
-      </c>
-      <c r="C122" t="s">
+      <c r="B122" s="3" t="s">
+        <v>4656</v>
+      </c>
+      <c r="C122" s="3" t="s">
         <v>649</v>
       </c>
-      <c r="D122" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D122" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A123" s="3" t="s">
         <v>650</v>
       </c>
-      <c r="B123" t="s">
-        <v>701</v>
-      </c>
-      <c r="C123" t="s">
+      <c r="B123" s="3" t="s">
+        <v>4657</v>
+      </c>
+      <c r="C123" s="3" t="s">
         <v>652</v>
       </c>
-      <c r="D123" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D123" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A124" s="3" t="s">
         <v>4526</v>
       </c>
-      <c r="B124" t="s">
-        <v>703</v>
-      </c>
-      <c r="C124" t="s">
+      <c r="B124" s="3" t="s">
+        <v>4658</v>
+      </c>
+      <c r="C124" s="3" t="s">
         <v>939</v>
       </c>
-      <c r="D124" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D124" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="s">
         <v>654</v>
       </c>
-      <c r="B125" t="s">
-        <v>705</v>
-      </c>
-      <c r="C125" t="s">
+      <c r="B125" s="3" t="s">
+        <v>4659</v>
+      </c>
+      <c r="C125" s="3" t="s">
         <v>656</v>
       </c>
-      <c r="D125" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D125" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A126" s="3" t="s">
         <v>657</v>
       </c>
-      <c r="B126" t="s">
-        <v>708</v>
-      </c>
-      <c r="C126" t="s">
+      <c r="B126" s="3" t="s">
+        <v>4660</v>
+      </c>
+      <c r="C126" s="3" t="s">
         <v>659</v>
       </c>
-      <c r="D126" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D126" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
         <v>660</v>
       </c>
-      <c r="B127" t="s">
-        <v>711</v>
-      </c>
-      <c r="C127" t="s">
+      <c r="B127" s="3" t="s">
+        <v>4661</v>
+      </c>
+      <c r="C127" s="3" t="s">
         <v>662</v>
       </c>
-      <c r="D127" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D127" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A128" s="3" t="s">
         <v>4527</v>
       </c>
-      <c r="B128" t="s">
-        <v>713</v>
-      </c>
-      <c r="C128" t="s">
+      <c r="B128" s="3" t="s">
+        <v>4662</v>
+      </c>
+      <c r="C128" s="3" t="s">
         <v>940</v>
       </c>
-      <c r="D128" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D128" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A129" s="3" t="s">
         <v>664</v>
       </c>
-      <c r="B129" t="s">
-        <v>715</v>
-      </c>
-      <c r="C129" t="s">
+      <c r="B129" s="3" t="s">
+        <v>4663</v>
+      </c>
+      <c r="C129" s="3" t="s">
         <v>666</v>
       </c>
-      <c r="D129" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D129" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A130" s="3" t="s">
         <v>667</v>
       </c>
-      <c r="B130" t="s">
-        <v>718</v>
-      </c>
-      <c r="C130" t="s">
+      <c r="B130" s="3" t="s">
+        <v>4664</v>
+      </c>
+      <c r="C130" s="3" t="s">
         <v>669</v>
       </c>
-      <c r="D130" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D130" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A131" s="3" t="s">
         <v>670</v>
       </c>
-      <c r="B131" t="s">
-        <v>721</v>
-      </c>
-      <c r="C131" t="s">
+      <c r="B131" s="3" t="s">
+        <v>4665</v>
+      </c>
+      <c r="C131" s="3" t="s">
         <v>672</v>
       </c>
-      <c r="D131" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D131" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A132" s="3" t="s">
         <v>4528</v>
       </c>
-      <c r="B132" t="s">
-        <v>723</v>
-      </c>
-      <c r="C132" t="s">
+      <c r="B132" s="3" t="s">
+        <v>4666</v>
+      </c>
+      <c r="C132" s="3" t="s">
         <v>941</v>
       </c>
-      <c r="D132" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D132" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
         <v>674</v>
       </c>
-      <c r="B133" t="s">
-        <v>725</v>
-      </c>
-      <c r="C133" t="s">
+      <c r="B133" s="3" t="s">
+        <v>4667</v>
+      </c>
+      <c r="C133" s="3" t="s">
         <v>676</v>
       </c>
-      <c r="D133" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D133" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A134" s="3" t="s">
         <v>677</v>
       </c>
-      <c r="B134" t="s">
-        <v>4444</v>
-      </c>
-      <c r="C134" t="s">
+      <c r="B134" s="3" t="s">
+        <v>4668</v>
+      </c>
+      <c r="C134" s="3" t="s">
         <v>679</v>
       </c>
-      <c r="D134" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D134" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
         <v>680</v>
       </c>
-      <c r="B135" t="s">
-        <v>4446</v>
-      </c>
-      <c r="C135" t="s">
+      <c r="B135" s="3" t="s">
+        <v>4669</v>
+      </c>
+      <c r="C135" s="3" t="s">
         <v>682</v>
       </c>
-      <c r="D135" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D135" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A136" s="3" t="s">
         <v>4529</v>
       </c>
-      <c r="B136" t="s">
-        <v>4448</v>
-      </c>
-      <c r="C136" t="s">
+      <c r="B136" s="3" t="s">
+        <v>4670</v>
+      </c>
+      <c r="C136" s="3" t="s">
         <v>942</v>
       </c>
-      <c r="D136" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D136" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A137" s="3" t="s">
         <v>684</v>
       </c>
-      <c r="B137" t="s">
-        <v>4450</v>
-      </c>
-      <c r="C137" t="s">
+      <c r="B137" s="3" t="s">
+        <v>4671</v>
+      </c>
+      <c r="C137" s="3" t="s">
         <v>686</v>
       </c>
-      <c r="D137" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D137" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A138" s="3" t="s">
         <v>687</v>
       </c>
-      <c r="B138" t="s">
-        <v>4452</v>
-      </c>
-      <c r="C138" t="s">
+      <c r="B138" s="3" t="s">
+        <v>4672</v>
+      </c>
+      <c r="C138" s="3" t="s">
         <v>689</v>
       </c>
-      <c r="D138" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D138" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
         <v>690</v>
       </c>
-      <c r="B139" t="s">
-        <v>4454</v>
-      </c>
-      <c r="C139" t="s">
+      <c r="B139" s="3" t="s">
+        <v>4673</v>
+      </c>
+      <c r="C139" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="D139" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D139" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A140" s="3" t="s">
         <v>4530</v>
       </c>
-      <c r="B140" t="s">
-        <v>4456</v>
-      </c>
-      <c r="C140" t="s">
+      <c r="B140" s="3" t="s">
+        <v>4674</v>
+      </c>
+      <c r="C140" s="3" t="s">
         <v>943</v>
       </c>
-      <c r="D140" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D140" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="s">
         <v>694</v>
       </c>
-      <c r="B141" t="s">
-        <v>4458</v>
-      </c>
-      <c r="C141" t="s">
+      <c r="B141" s="3" t="s">
+        <v>4675</v>
+      </c>
+      <c r="C141" s="3" t="s">
         <v>696</v>
       </c>
-      <c r="D141" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D141" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A142" s="3" t="s">
         <v>697</v>
       </c>
-      <c r="B142" t="s">
-        <v>4460</v>
-      </c>
-      <c r="C142" t="s">
+      <c r="B142" s="3" t="s">
+        <v>4676</v>
+      </c>
+      <c r="C142" s="3" t="s">
         <v>699</v>
       </c>
-      <c r="D142" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D142" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A143" s="3" t="s">
         <v>700</v>
       </c>
-      <c r="B143" t="s">
-        <v>4462</v>
-      </c>
-      <c r="C143" t="s">
+      <c r="B143" s="3" t="s">
+        <v>4677</v>
+      </c>
+      <c r="C143" s="3" t="s">
         <v>702</v>
       </c>
-      <c r="D143" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D143" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A144" s="3" t="s">
         <v>4531</v>
       </c>
-      <c r="B144" t="s">
-        <v>4464</v>
-      </c>
-      <c r="C144" t="s">
+      <c r="B144" s="3" t="s">
+        <v>4678</v>
+      </c>
+      <c r="C144" s="3" t="s">
         <v>944</v>
       </c>
-      <c r="D144" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D144" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A145" s="3" t="s">
         <v>704</v>
       </c>
-      <c r="B145" t="s">
-        <v>4466</v>
-      </c>
-      <c r="C145" t="s">
+      <c r="B145" s="3" t="s">
+        <v>4679</v>
+      </c>
+      <c r="C145" s="3" t="s">
         <v>706</v>
       </c>
-      <c r="D145" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D145" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A146" s="3" t="s">
         <v>707</v>
       </c>
-      <c r="B146" t="s">
-        <v>728</v>
-      </c>
-      <c r="C146" t="s">
+      <c r="B146" s="3" t="s">
+        <v>4680</v>
+      </c>
+      <c r="C146" s="3" t="s">
         <v>4624</v>
       </c>
-      <c r="D146" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D146" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="s">
         <v>710</v>
       </c>
-      <c r="B147" t="s">
-        <v>730</v>
-      </c>
-      <c r="C147" t="s">
+      <c r="B147" s="3" t="s">
+        <v>4681</v>
+      </c>
+      <c r="C147" s="3" t="s">
         <v>4625</v>
       </c>
-      <c r="D147" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D147" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A148" s="3" t="s">
         <v>4532</v>
       </c>
-      <c r="B148" t="s">
-        <v>731</v>
-      </c>
-      <c r="C148" t="s">
+      <c r="B148" s="3" t="s">
+        <v>4682</v>
+      </c>
+      <c r="C148" s="3" t="s">
         <v>4626</v>
       </c>
-      <c r="D148" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D148" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="s">
         <v>714</v>
       </c>
-      <c r="B149" t="s">
-        <v>733</v>
-      </c>
-      <c r="C149" t="s">
+      <c r="B149" s="3" t="s">
+        <v>4683</v>
+      </c>
+      <c r="C149" s="3" t="s">
         <v>4627</v>
       </c>
-      <c r="D149" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D149" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A150" s="3" t="s">
         <v>717</v>
       </c>
-      <c r="B150" t="s">
-        <v>4468</v>
-      </c>
-      <c r="C150" t="s">
+      <c r="B150" s="3" t="s">
+        <v>4684</v>
+      </c>
+      <c r="C150" s="3" t="s">
         <v>4632</v>
       </c>
-      <c r="D150" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D150" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A151" s="3" t="s">
         <v>720</v>
       </c>
-      <c r="B151" t="s">
-        <v>4470</v>
-      </c>
-      <c r="C151" t="s">
+      <c r="B151" s="3" t="s">
+        <v>4685</v>
+      </c>
+      <c r="C151" s="3" t="s">
         <v>4633</v>
       </c>
-      <c r="D151" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D151" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A152" s="3" t="s">
         <v>4533</v>
       </c>
-      <c r="B152" t="s">
-        <v>4472</v>
-      </c>
-      <c r="C152" t="s">
+      <c r="B152" s="3" t="s">
+        <v>4686</v>
+      </c>
+      <c r="C152" s="3" t="s">
         <v>4634</v>
       </c>
-      <c r="D152" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D152" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A153" s="3" t="s">
         <v>724</v>
       </c>
-      <c r="B153" t="s">
-        <v>4474</v>
-      </c>
-      <c r="C153" t="s">
+      <c r="B153" s="3" t="s">
+        <v>4687</v>
+      </c>
+      <c r="C153" s="3" t="s">
         <v>4635</v>
       </c>
-      <c r="D153" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D153" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A154" s="3" t="s">
         <v>727</v>
       </c>
-      <c r="B154" t="s">
-        <v>4648</v>
-      </c>
-      <c r="C154" t="s">
+      <c r="B154" s="3" t="s">
+        <v>4688</v>
+      </c>
+      <c r="C154" s="3" t="s">
         <v>751</v>
       </c>
-      <c r="D154" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D154" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A155" s="3" t="s">
         <v>729</v>
       </c>
-      <c r="B155" t="s">
-        <v>4649</v>
-      </c>
-      <c r="C155" t="s">
+      <c r="B155" s="3" t="s">
+        <v>4689</v>
+      </c>
+      <c r="C155" s="3" t="s">
         <v>752</v>
       </c>
-      <c r="D155" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D155" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A156" s="3" t="s">
         <v>4534</v>
       </c>
-      <c r="B156" t="s">
-        <v>4650</v>
-      </c>
-      <c r="C156" t="s">
+      <c r="B156" s="3" t="s">
+        <v>4690</v>
+      </c>
+      <c r="C156" s="3" t="s">
         <v>947</v>
       </c>
-      <c r="D156" t="s">
+      <c r="D156" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A157" s="3" t="s">
+      <c r="A157" t="s">
         <v>732</v>
       </c>
       <c r="B157" t="s">
-        <v>4651</v>
+        <v>4691</v>
       </c>
       <c r="C157" t="s">
         <v>753</v>
@@ -19314,7 +19434,7 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" t="s">
         <v>387</v>
       </c>
       <c r="B2" t="s">
@@ -19328,7 +19448,7 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" t="s">
         <v>390</v>
       </c>
       <c r="B3" t="s">
@@ -19342,7 +19462,7 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+      <c r="A4" t="s">
         <v>4484</v>
       </c>
       <c r="B4" t="s">
@@ -19356,7 +19476,7 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+      <c r="A5" t="s">
         <v>394</v>
       </c>
       <c r="B5" t="s">
@@ -19370,7 +19490,7 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
+      <c r="A6" t="s">
         <v>397</v>
       </c>
       <c r="B6" t="s">
@@ -19384,7 +19504,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
+      <c r="A7" t="s">
         <v>400</v>
       </c>
       <c r="B7" t="s">
@@ -19398,7 +19518,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
+      <c r="A8" t="s">
         <v>4485</v>
       </c>
       <c r="B8" t="s">
@@ -19412,7 +19532,7 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
+      <c r="A9" t="s">
         <v>404</v>
       </c>
       <c r="B9" t="s">
@@ -19426,7 +19546,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
+      <c r="A10" t="s">
         <v>407</v>
       </c>
       <c r="B10" t="s">
@@ -19440,7 +19560,7 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
+      <c r="A11" t="s">
         <v>410</v>
       </c>
       <c r="B11" t="s">
@@ -19454,7 +19574,7 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
+      <c r="A12" t="s">
         <v>4486</v>
       </c>
       <c r="B12" t="s">
@@ -19468,7 +19588,7 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
+      <c r="A13" t="s">
         <v>414</v>
       </c>
       <c r="B13" t="s">
@@ -19482,7 +19602,7 @@
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
+      <c r="A14" t="s">
         <v>417</v>
       </c>
       <c r="B14" t="s">
@@ -19496,7 +19616,7 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
+      <c r="A15" t="s">
         <v>420</v>
       </c>
       <c r="B15" t="s">
@@ -19510,7 +19630,7 @@
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
+      <c r="A16" t="s">
         <v>4487</v>
       </c>
       <c r="B16" t="s">
@@ -19524,7 +19644,7 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
+      <c r="A17" t="s">
         <v>424</v>
       </c>
       <c r="B17" t="s">
@@ -19538,7 +19658,7 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
+      <c r="A18" t="s">
         <v>427</v>
       </c>
       <c r="B18" t="s">
@@ -19552,7 +19672,7 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
+      <c r="A19" t="s">
         <v>430</v>
       </c>
       <c r="B19" t="s">
@@ -19566,7 +19686,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="s">
+      <c r="A20" t="s">
         <v>4488</v>
       </c>
       <c r="B20" t="s">
@@ -19580,7 +19700,7 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="3" t="s">
+      <c r="A21" t="s">
         <v>434</v>
       </c>
       <c r="B21" t="s">
@@ -19594,7 +19714,7 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="3" t="s">
+      <c r="A22" t="s">
         <v>437</v>
       </c>
       <c r="B22" t="s">
@@ -19608,7 +19728,7 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="3" t="s">
+      <c r="A23" t="s">
         <v>440</v>
       </c>
       <c r="B23" t="s">
@@ -19622,7 +19742,7 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="3" t="s">
+      <c r="A24" t="s">
         <v>4489</v>
       </c>
       <c r="B24" t="s">
@@ -19636,7 +19756,7 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="3" t="s">
+      <c r="A25" t="s">
         <v>444</v>
       </c>
       <c r="B25" t="s">
@@ -19650,7 +19770,7 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="3" t="s">
+      <c r="A26" t="s">
         <v>447</v>
       </c>
       <c r="B26" t="s">
@@ -19664,7 +19784,7 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="3" t="s">
+      <c r="A27" t="s">
         <v>450</v>
       </c>
       <c r="B27" t="s">
@@ -19678,7 +19798,7 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="3" t="s">
+      <c r="A28" t="s">
         <v>4490</v>
       </c>
       <c r="B28" t="s">
@@ -19692,7 +19812,7 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="3" t="s">
+      <c r="A29" t="s">
         <v>454</v>
       </c>
       <c r="B29" t="s">
@@ -19706,7 +19826,7 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="3" t="s">
+      <c r="A30" t="s">
         <v>457</v>
       </c>
       <c r="B30" t="s">
@@ -19720,7 +19840,7 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="3" t="s">
+      <c r="A31" t="s">
         <v>460</v>
       </c>
       <c r="B31" t="s">
@@ -19734,7 +19854,7 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="3" t="s">
+      <c r="A32" t="s">
         <v>4491</v>
       </c>
       <c r="B32" t="s">
@@ -19748,7 +19868,7 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="3" t="s">
+      <c r="A33" t="s">
         <v>464</v>
       </c>
       <c r="B33" t="s">
@@ -19762,7 +19882,7 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="3" t="s">
+      <c r="A34" t="s">
         <v>467</v>
       </c>
       <c r="B34" t="s">
@@ -19776,7 +19896,7 @@
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="3" t="s">
+      <c r="A35" t="s">
         <v>470</v>
       </c>
       <c r="B35" t="s">
@@ -19790,7 +19910,7 @@
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="3" t="s">
+      <c r="A36" t="s">
         <v>4492</v>
       </c>
       <c r="B36" t="s">
@@ -19804,7 +19924,7 @@
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="3" t="s">
+      <c r="A37" t="s">
         <v>474</v>
       </c>
       <c r="B37" t="s">
@@ -19818,7 +19938,7 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="3" t="s">
+      <c r="A38" t="s">
         <v>4493</v>
       </c>
       <c r="B38" t="s">
@@ -19832,7 +19952,7 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="3" t="s">
+      <c r="A39" t="s">
         <v>4494</v>
       </c>
       <c r="B39" t="s">
@@ -19846,7 +19966,7 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="3" t="s">
+      <c r="A40" t="s">
         <v>4495</v>
       </c>
       <c r="B40" t="s">
@@ -19860,7 +19980,7 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" s="3" t="s">
+      <c r="A41" t="s">
         <v>4496</v>
       </c>
       <c r="B41" t="s">
@@ -19874,7 +19994,7 @@
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" s="3" t="s">
+      <c r="A42" t="s">
         <v>477</v>
       </c>
       <c r="B42" t="s">
@@ -19888,7 +20008,7 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" s="3" t="s">
+      <c r="A43" t="s">
         <v>480</v>
       </c>
       <c r="B43" t="s">
@@ -19902,7 +20022,7 @@
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" s="3" t="s">
+      <c r="A44" t="s">
         <v>4497</v>
       </c>
       <c r="B44" t="s">
@@ -19916,7 +20036,7 @@
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" s="3" t="s">
+      <c r="A45" t="s">
         <v>484</v>
       </c>
       <c r="B45" t="s">
@@ -19930,7 +20050,7 @@
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46" s="3" t="s">
+      <c r="A46" t="s">
         <v>487</v>
       </c>
       <c r="B46" t="s">
@@ -19944,7 +20064,7 @@
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47" s="3" t="s">
+      <c r="A47" t="s">
         <v>488</v>
       </c>
       <c r="B47" t="s">
@@ -19958,7 +20078,7 @@
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" s="3" t="s">
+      <c r="A48" t="s">
         <v>4498</v>
       </c>
       <c r="B48" t="s">
@@ -19972,7 +20092,7 @@
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A49" s="3" t="s">
+      <c r="A49" t="s">
         <v>489</v>
       </c>
       <c r="B49" t="s">
@@ -19986,7 +20106,7 @@
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A50" s="3" t="s">
+      <c r="A50" t="s">
         <v>497</v>
       </c>
       <c r="B50" t="s">
@@ -20000,7 +20120,7 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A51" s="3" t="s">
+      <c r="A51" t="s">
         <v>500</v>
       </c>
       <c r="B51" t="s">
@@ -20014,7 +20134,7 @@
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A52" s="3" t="s">
+      <c r="A52" t="s">
         <v>4499</v>
       </c>
       <c r="B52" t="s">
@@ -20028,7 +20148,7 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A53" s="3" t="s">
+      <c r="A53" t="s">
         <v>504</v>
       </c>
       <c r="B53" t="s">
@@ -20042,7 +20162,7 @@
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A54" s="3" t="s">
+      <c r="A54" t="s">
         <v>507</v>
       </c>
       <c r="B54" t="s">
@@ -20056,7 +20176,7 @@
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A55" s="3" t="s">
+      <c r="A55" t="s">
         <v>510</v>
       </c>
       <c r="B55" t="s">
@@ -20070,7 +20190,7 @@
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A56" s="3" t="s">
+      <c r="A56" t="s">
         <v>4500</v>
       </c>
       <c r="B56" t="s">
@@ -20084,7 +20204,7 @@
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A57" s="3" t="s">
+      <c r="A57" t="s">
         <v>514</v>
       </c>
       <c r="B57" t="s">
@@ -20098,7 +20218,7 @@
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58" s="3" t="s">
+      <c r="A58" t="s">
         <v>517</v>
       </c>
       <c r="B58" t="s">
@@ -20112,7 +20232,7 @@
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A59" s="3" t="s">
+      <c r="A59" t="s">
         <v>520</v>
       </c>
       <c r="B59" t="s">
@@ -20126,7 +20246,7 @@
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A60" s="3" t="s">
+      <c r="A60" t="s">
         <v>4501</v>
       </c>
       <c r="B60" t="s">
@@ -20140,7 +20260,7 @@
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A61" s="3" t="s">
+      <c r="A61" t="s">
         <v>524</v>
       </c>
       <c r="B61" t="s">
@@ -20154,7 +20274,7 @@
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A62" s="3" t="s">
+      <c r="A62" t="s">
         <v>527</v>
       </c>
       <c r="B62" t="s">
@@ -20168,7 +20288,7 @@
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A63" s="3" t="s">
+      <c r="A63" t="s">
         <v>528</v>
       </c>
       <c r="B63" t="s">
@@ -20182,7 +20302,7 @@
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A64" s="3" t="s">
+      <c r="A64" t="s">
         <v>4502</v>
       </c>
       <c r="B64" t="s">
@@ -20196,7 +20316,7 @@
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A65" s="3" t="s">
+      <c r="A65" t="s">
         <v>529</v>
       </c>
       <c r="B65" t="s">
@@ -20210,7 +20330,7 @@
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A66" s="3" t="s">
+      <c r="A66" t="s">
         <v>4503</v>
       </c>
       <c r="B66" t="s">
@@ -20224,7 +20344,7 @@
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A67" s="3" t="s">
+      <c r="A67" t="s">
         <v>4504</v>
       </c>
       <c r="B67" t="s">
@@ -20238,7 +20358,7 @@
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A68" s="3" t="s">
+      <c r="A68" t="s">
         <v>4505</v>
       </c>
       <c r="B68" t="s">
@@ -20252,7 +20372,7 @@
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A69" s="3" t="s">
+      <c r="A69" t="s">
         <v>4506</v>
       </c>
       <c r="B69" t="s">
@@ -20266,7 +20386,7 @@
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A70" s="3" t="s">
+      <c r="A70" t="s">
         <v>4507</v>
       </c>
       <c r="B70" t="s">
@@ -20280,7 +20400,7 @@
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A71" s="3" t="s">
+      <c r="A71" t="s">
         <v>4508</v>
       </c>
       <c r="B71" t="s">
@@ -20294,7 +20414,7 @@
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A72" s="3" t="s">
+      <c r="A72" t="s">
         <v>4509</v>
       </c>
       <c r="B72" t="s">
@@ -20308,7 +20428,7 @@
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A73" s="3" t="s">
+      <c r="A73" t="s">
         <v>4510</v>
       </c>
       <c r="B73" t="s">
@@ -20322,7 +20442,7 @@
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A74" s="3" t="s">
+      <c r="A74" t="s">
         <v>4511</v>
       </c>
       <c r="B74" t="s">
@@ -20336,7 +20456,7 @@
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A75" s="3" t="s">
+      <c r="A75" t="s">
         <v>4512</v>
       </c>
       <c r="B75" t="s">
@@ -20350,7 +20470,7 @@
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A76" s="3" t="s">
+      <c r="A76" t="s">
         <v>4513</v>
       </c>
       <c r="B76" t="s">
@@ -20364,7 +20484,7 @@
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A77" s="3" t="s">
+      <c r="A77" t="s">
         <v>4514</v>
       </c>
       <c r="B77" t="s">
@@ -20378,7 +20498,7 @@
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A78" s="3" t="s">
+      <c r="A78" t="s">
         <v>537</v>
       </c>
       <c r="B78" t="s">
@@ -20392,7 +20512,7 @@
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A79" s="3" t="s">
+      <c r="A79" t="s">
         <v>540</v>
       </c>
       <c r="B79" t="s">
@@ -20406,7 +20526,7 @@
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A80" s="3" t="s">
+      <c r="A80" t="s">
         <v>4515</v>
       </c>
       <c r="B80" t="s">
@@ -20420,7 +20540,7 @@
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A81" s="3" t="s">
+      <c r="A81" t="s">
         <v>544</v>
       </c>
       <c r="B81" t="s">
@@ -20434,7 +20554,7 @@
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A82" s="3" t="s">
+      <c r="A82" t="s">
         <v>547</v>
       </c>
       <c r="B82" t="s">
@@ -20448,7 +20568,7 @@
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A83" s="3" t="s">
+      <c r="A83" t="s">
         <v>550</v>
       </c>
       <c r="B83" t="s">
@@ -20462,7 +20582,7 @@
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A84" s="3" t="s">
+      <c r="A84" t="s">
         <v>4516</v>
       </c>
       <c r="B84" t="s">
@@ -20476,7 +20596,7 @@
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A85" s="3" t="s">
+      <c r="A85" t="s">
         <v>554</v>
       </c>
       <c r="B85" t="s">
@@ -20490,7 +20610,7 @@
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A86" s="3" t="s">
+      <c r="A86" t="s">
         <v>557</v>
       </c>
       <c r="B86" t="s">
@@ -20504,7 +20624,7 @@
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A87" s="3" t="s">
+      <c r="A87" t="s">
         <v>560</v>
       </c>
       <c r="B87" t="s">
@@ -20518,7 +20638,7 @@
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A88" s="3" t="s">
+      <c r="A88" t="s">
         <v>4517</v>
       </c>
       <c r="B88" t="s">
@@ -20532,7 +20652,7 @@
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A89" s="3" t="s">
+      <c r="A89" t="s">
         <v>564</v>
       </c>
       <c r="B89" t="s">
@@ -20546,7 +20666,7 @@
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A90" s="3" t="s">
+      <c r="A90" t="s">
         <v>567</v>
       </c>
       <c r="B90" t="s">
@@ -20560,7 +20680,7 @@
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A91" s="3" t="s">
+      <c r="A91" t="s">
         <v>570</v>
       </c>
       <c r="B91" t="s">
@@ -20574,7 +20694,7 @@
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A92" s="3" t="s">
+      <c r="A92" t="s">
         <v>4518</v>
       </c>
       <c r="B92" t="s">
@@ -20588,7 +20708,7 @@
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A93" s="3" t="s">
+      <c r="A93" t="s">
         <v>574</v>
       </c>
       <c r="B93" t="s">
@@ -20602,7 +20722,7 @@
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A94" s="3" t="s">
+      <c r="A94" t="s">
         <v>577</v>
       </c>
       <c r="B94" t="s">
@@ -20616,7 +20736,7 @@
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A95" s="3" t="s">
+      <c r="A95" t="s">
         <v>580</v>
       </c>
       <c r="B95" t="s">
@@ -20630,7 +20750,7 @@
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A96" s="3" t="s">
+      <c r="A96" t="s">
         <v>4519</v>
       </c>
       <c r="B96" t="s">
@@ -20644,7 +20764,7 @@
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A97" s="3" t="s">
+      <c r="A97" t="s">
         <v>584</v>
       </c>
       <c r="B97" t="s">
@@ -20658,7 +20778,7 @@
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A98" s="3" t="s">
+      <c r="A98" t="s">
         <v>587</v>
       </c>
       <c r="B98" t="s">
@@ -20672,7 +20792,7 @@
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A99" s="3" t="s">
+      <c r="A99" t="s">
         <v>590</v>
       </c>
       <c r="B99" t="s">
@@ -20686,7 +20806,7 @@
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A100" s="3" t="s">
+      <c r="A100" t="s">
         <v>4520</v>
       </c>
       <c r="B100" t="s">
@@ -20700,7 +20820,7 @@
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A101" s="3" t="s">
+      <c r="A101" t="s">
         <v>594</v>
       </c>
       <c r="B101" t="s">
@@ -20714,7 +20834,7 @@
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A102" s="3" t="s">
+      <c r="A102" t="s">
         <v>597</v>
       </c>
       <c r="B102" t="s">
@@ -20728,7 +20848,7 @@
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A103" s="3" t="s">
+      <c r="A103" t="s">
         <v>600</v>
       </c>
       <c r="B103" t="s">
@@ -20742,7 +20862,7 @@
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A104" s="3" t="s">
+      <c r="A104" t="s">
         <v>4521</v>
       </c>
       <c r="B104" t="s">
@@ -20756,7 +20876,7 @@
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A105" s="3" t="s">
+      <c r="A105" t="s">
         <v>604</v>
       </c>
       <c r="B105" t="s">
@@ -20770,7 +20890,7 @@
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A106" s="3" t="s">
+      <c r="A106" t="s">
         <v>607</v>
       </c>
       <c r="B106" t="s">
@@ -20784,7 +20904,7 @@
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A107" s="3" t="s">
+      <c r="A107" t="s">
         <v>610</v>
       </c>
       <c r="B107" t="s">
@@ -20798,7 +20918,7 @@
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A108" s="3" t="s">
+      <c r="A108" t="s">
         <v>4522</v>
       </c>
       <c r="B108" t="s">
@@ -20812,7 +20932,7 @@
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A109" s="3" t="s">
+      <c r="A109" t="s">
         <v>614</v>
       </c>
       <c r="B109" t="s">
@@ -20826,7 +20946,7 @@
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A110" s="3" t="s">
+      <c r="A110" t="s">
         <v>617</v>
       </c>
       <c r="B110" t="s">
@@ -20840,7 +20960,7 @@
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A111" s="3" t="s">
+      <c r="A111" t="s">
         <v>620</v>
       </c>
       <c r="B111" t="s">
@@ -20854,7 +20974,7 @@
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A112" s="3" t="s">
+      <c r="A112" t="s">
         <v>4523</v>
       </c>
       <c r="B112" t="s">
@@ -20868,7 +20988,7 @@
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A113" s="3" t="s">
+      <c r="A113" t="s">
         <v>624</v>
       </c>
       <c r="B113" t="s">
@@ -20882,7 +21002,7 @@
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A114" s="3" t="s">
+      <c r="A114" t="s">
         <v>627</v>
       </c>
       <c r="B114" t="s">
@@ -20896,7 +21016,7 @@
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A115" s="3" t="s">
+      <c r="A115" t="s">
         <v>630</v>
       </c>
       <c r="B115" t="s">
@@ -20910,7 +21030,7 @@
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A116" s="3" t="s">
+      <c r="A116" t="s">
         <v>4524</v>
       </c>
       <c r="B116" t="s">
@@ -20924,7 +21044,7 @@
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A117" s="3" t="s">
+      <c r="A117" t="s">
         <v>634</v>
       </c>
       <c r="B117" t="s">
@@ -20938,7 +21058,7 @@
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A118" s="3" t="s">
+      <c r="A118" t="s">
         <v>637</v>
       </c>
       <c r="B118" t="s">
@@ -20952,7 +21072,7 @@
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A119" s="3" t="s">
+      <c r="A119" t="s">
         <v>640</v>
       </c>
       <c r="B119" t="s">
@@ -20966,7 +21086,7 @@
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A120" s="3" t="s">
+      <c r="A120" t="s">
         <v>4525</v>
       </c>
       <c r="B120" t="s">
@@ -20980,7 +21100,7 @@
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A121" s="3" t="s">
+      <c r="A121" t="s">
         <v>644</v>
       </c>
       <c r="B121" t="s">
@@ -20994,7 +21114,7 @@
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A122" s="3" t="s">
+      <c r="A122" t="s">
         <v>647</v>
       </c>
       <c r="B122" t="s">
@@ -21008,7 +21128,7 @@
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A123" s="3" t="s">
+      <c r="A123" t="s">
         <v>650</v>
       </c>
       <c r="B123" t="s">
@@ -21022,7 +21142,7 @@
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A124" s="3" t="s">
+      <c r="A124" t="s">
         <v>4526</v>
       </c>
       <c r="B124" t="s">
@@ -21036,7 +21156,7 @@
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A125" s="3" t="s">
+      <c r="A125" t="s">
         <v>654</v>
       </c>
       <c r="B125" t="s">
@@ -21050,7 +21170,7 @@
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A126" s="3" t="s">
+      <c r="A126" t="s">
         <v>657</v>
       </c>
       <c r="B126" t="s">
@@ -21064,7 +21184,7 @@
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A127" s="3" t="s">
+      <c r="A127" t="s">
         <v>660</v>
       </c>
       <c r="B127" t="s">
@@ -21078,7 +21198,7 @@
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A128" s="3" t="s">
+      <c r="A128" t="s">
         <v>4527</v>
       </c>
       <c r="B128" t="s">
@@ -21092,7 +21212,7 @@
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A129" s="3" t="s">
+      <c r="A129" t="s">
         <v>664</v>
       </c>
       <c r="B129" t="s">
@@ -21106,7 +21226,7 @@
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A130" s="3" t="s">
+      <c r="A130" t="s">
         <v>667</v>
       </c>
       <c r="B130" t="s">
@@ -21120,7 +21240,7 @@
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A131" s="3" t="s">
+      <c r="A131" t="s">
         <v>670</v>
       </c>
       <c r="B131" t="s">
@@ -21134,7 +21254,7 @@
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A132" s="3" t="s">
+      <c r="A132" t="s">
         <v>4528</v>
       </c>
       <c r="B132" t="s">
@@ -21148,7 +21268,7 @@
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A133" s="3" t="s">
+      <c r="A133" t="s">
         <v>674</v>
       </c>
       <c r="B133" t="s">
@@ -21162,7 +21282,7 @@
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A134" s="3" t="s">
+      <c r="A134" t="s">
         <v>677</v>
       </c>
       <c r="B134" t="s">
@@ -21176,7 +21296,7 @@
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A135" s="3" t="s">
+      <c r="A135" t="s">
         <v>680</v>
       </c>
       <c r="B135" t="s">
@@ -21190,7 +21310,7 @@
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A136" s="3" t="s">
+      <c r="A136" t="s">
         <v>4529</v>
       </c>
       <c r="B136" t="s">
@@ -21204,7 +21324,7 @@
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A137" s="3" t="s">
+      <c r="A137" t="s">
         <v>684</v>
       </c>
       <c r="B137" t="s">
@@ -21218,7 +21338,7 @@
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A138" s="3" t="s">
+      <c r="A138" t="s">
         <v>687</v>
       </c>
       <c r="B138" t="s">
@@ -21232,7 +21352,7 @@
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A139" s="3" t="s">
+      <c r="A139" t="s">
         <v>690</v>
       </c>
       <c r="B139" t="s">
@@ -21246,7 +21366,7 @@
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A140" s="3" t="s">
+      <c r="A140" t="s">
         <v>4530</v>
       </c>
       <c r="B140" t="s">
@@ -21260,7 +21380,7 @@
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A141" s="3" t="s">
+      <c r="A141" t="s">
         <v>694</v>
       </c>
       <c r="B141" t="s">
@@ -21274,7 +21394,7 @@
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A142" s="3" t="s">
+      <c r="A142" t="s">
         <v>697</v>
       </c>
       <c r="B142" t="s">
@@ -21288,7 +21408,7 @@
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A143" s="3" t="s">
+      <c r="A143" t="s">
         <v>700</v>
       </c>
       <c r="B143" t="s">
@@ -21302,7 +21422,7 @@
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A144" s="3" t="s">
+      <c r="A144" t="s">
         <v>4531</v>
       </c>
       <c r="B144" t="s">
@@ -21316,7 +21436,7 @@
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A145" s="3" t="s">
+      <c r="A145" t="s">
         <v>704</v>
       </c>
       <c r="B145" t="s">
@@ -21330,7 +21450,7 @@
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A146" s="3" t="s">
+      <c r="A146" t="s">
         <v>707</v>
       </c>
       <c r="B146" t="s">
@@ -21344,7 +21464,7 @@
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A147" s="3" t="s">
+      <c r="A147" t="s">
         <v>710</v>
       </c>
       <c r="B147" t="s">
@@ -21358,7 +21478,7 @@
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A148" s="3" t="s">
+      <c r="A148" t="s">
         <v>4532</v>
       </c>
       <c r="B148" t="s">
@@ -21372,7 +21492,7 @@
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A149" s="3" t="s">
+      <c r="A149" t="s">
         <v>714</v>
       </c>
       <c r="B149" t="s">
@@ -21386,7 +21506,7 @@
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A150" s="3" t="s">
+      <c r="A150" t="s">
         <v>717</v>
       </c>
       <c r="B150" t="s">
@@ -21400,7 +21520,7 @@
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A151" s="3" t="s">
+      <c r="A151" t="s">
         <v>720</v>
       </c>
       <c r="B151" t="s">
@@ -21414,7 +21534,7 @@
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A152" s="3" t="s">
+      <c r="A152" t="s">
         <v>4533</v>
       </c>
       <c r="B152" t="s">
@@ -21428,7 +21548,7 @@
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A153" s="3" t="s">
+      <c r="A153" t="s">
         <v>724</v>
       </c>
       <c r="B153" t="s">
@@ -21442,7 +21562,7 @@
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A154" s="3" t="s">
+      <c r="A154" t="s">
         <v>727</v>
       </c>
       <c r="B154" t="s">
@@ -21456,7 +21576,7 @@
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A155" s="3" t="s">
+      <c r="A155" t="s">
         <v>729</v>
       </c>
       <c r="B155" t="s">
@@ -21470,7 +21590,7 @@
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A156" s="3" t="s">
+      <c r="A156" t="s">
         <v>4534</v>
       </c>
       <c r="B156" t="s">
@@ -21484,7 +21604,7 @@
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A157" s="3" t="s">
+      <c r="A157" t="s">
         <v>732</v>
       </c>
       <c r="B157" t="s">
@@ -22012,7 +22132,7 @@
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:A216">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A216">
     <sortCondition ref="A2:A216"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
